--- a/pages/video_analysis/IP_Master_Men.xlsx
+++ b/pages/video_analysis/IP_Master_Men.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F69781-7BC1-48DB-B1AE-D7148BE8E59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3921B2E9-D6A1-42CD-AA72-D4414B72E78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$65</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -137,7 +140,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -446,6 +449,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1955,6 +1969,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J65" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J65">
+      <sortCondition descending="1" ref="B1:B65"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/video_analysis/IP_Master_Men.xlsx
+++ b/pages/video_analysis/IP_Master_Men.xlsx
@@ -5,25 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3921B2E9-D6A1-42CD-AA72-D4414B72E78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9F7607-0B3F-4B96-B388-D89298914905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="0" windowWidth="9612" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1008" windowWidth="11256" windowHeight="11952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$65</definedName>
-  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="15">
   <si>
     <t>Title</t>
   </si>
@@ -49,19 +46,25 @@
     <t>Video</t>
   </si>
   <si>
+    <t>SRM_File</t>
+  </si>
+  <si>
     <t>27/7/2023 Keegan Hornblow Grenchen</t>
+  </si>
+  <si>
+    <t>6/8/2023 Tom Sexton Q Glasgow WCH</t>
   </si>
   <si>
     <t>No Change</t>
   </si>
   <si>
+    <t>https://youtu.be/n4bAB6UxK90</t>
+  </si>
+  <si>
     <t>Campbell_Bunch_test</t>
   </si>
   <si>
-    <t>SRM_File</t>
-  </si>
-  <si>
-    <t>https://youtu.be/n4bAB6UxK90</t>
+    <t>https://youtu.be/kMm4Y9rzpyc</t>
   </si>
 </sst>
 </file>
@@ -71,7 +74,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +90,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -96,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,20 +129,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -140,11 +143,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -447,18 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -486,13 +480,13 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>11</v>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>45134</v>
@@ -510,18 +504,18 @@
         <v>25.63</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2">
         <v>45134</v>
@@ -539,12 +533,12 @@
         <v>46.88</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <v>45134</v>
@@ -562,12 +556,12 @@
         <v>54.35</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>45134</v>
@@ -585,12 +579,12 @@
         <v>56.82</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2">
         <v>45134</v>
@@ -608,12 +602,12 @@
         <v>57.99</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2">
         <v>45134</v>
@@ -631,12 +625,12 @@
         <v>58.59</v>
       </c>
       <c r="G7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
         <v>45134</v>
@@ -654,12 +648,12 @@
         <v>58.59</v>
       </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>45134</v>
@@ -677,12 +671,12 @@
         <v>58.59</v>
       </c>
       <c r="G9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>45134</v>
@@ -700,12 +694,12 @@
         <v>58.59</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
         <v>45134</v>
@@ -723,12 +717,12 @@
         <v>59.21</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2">
         <v>45134</v>
@@ -746,12 +740,12 @@
         <v>58.59</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2">
         <v>45134</v>
@@ -769,12 +763,12 @@
         <v>58.9</v>
       </c>
       <c r="G13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2">
         <v>45134</v>
@@ -792,12 +786,12 @@
         <v>58.9</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2">
         <v>45134</v>
@@ -815,12 +809,12 @@
         <v>59.21</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2">
         <v>45134</v>
@@ -838,12 +832,12 @@
         <v>58.9</v>
       </c>
       <c r="G16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2">
         <v>45134</v>
@@ -861,12 +855,12 @@
         <v>58.59</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2">
         <v>45134</v>
@@ -884,12 +878,12 @@
         <v>58.59</v>
       </c>
       <c r="G18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2">
         <v>45134</v>
@@ -907,12 +901,12 @@
         <v>58.59</v>
       </c>
       <c r="G19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2">
         <v>45134</v>
@@ -930,12 +924,12 @@
         <v>58.9</v>
       </c>
       <c r="G20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2">
         <v>45134</v>
@@ -953,12 +947,12 @@
         <v>58.59</v>
       </c>
       <c r="G21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2">
         <v>45134</v>
@@ -976,12 +970,12 @@
         <v>58.9</v>
       </c>
       <c r="G22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2">
         <v>45134</v>
@@ -999,12 +993,12 @@
         <v>59.21</v>
       </c>
       <c r="G23" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2">
         <v>45134</v>
@@ -1022,12 +1016,12 @@
         <v>58.9</v>
       </c>
       <c r="G24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2">
         <v>45134</v>
@@ -1045,12 +1039,12 @@
         <v>58.9</v>
       </c>
       <c r="G25" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B26" s="2">
         <v>45134</v>
@@ -1068,12 +1062,12 @@
         <v>58.9</v>
       </c>
       <c r="G26" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2">
         <v>45134</v>
@@ -1091,12 +1085,12 @@
         <v>58.9</v>
       </c>
       <c r="G27" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2">
         <v>45134</v>
@@ -1114,12 +1108,12 @@
         <v>58.9</v>
       </c>
       <c r="G28" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2">
         <v>45134</v>
@@ -1137,12 +1131,12 @@
         <v>58.29</v>
       </c>
       <c r="G29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B30" s="2">
         <v>45134</v>
@@ -1160,12 +1154,12 @@
         <v>58.59</v>
       </c>
       <c r="G30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2">
         <v>45134</v>
@@ -1183,12 +1177,12 @@
         <v>58.59</v>
       </c>
       <c r="G31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2">
         <v>45134</v>
@@ -1206,12 +1200,12 @@
         <v>58.9</v>
       </c>
       <c r="G32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2">
         <v>45134</v>
@@ -1229,12 +1223,12 @@
         <v>58.29</v>
       </c>
       <c r="G33" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2">
         <v>45134</v>
@@ -1252,12 +1246,12 @@
         <v>57.99</v>
       </c>
       <c r="G34" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2">
         <v>45134</v>
@@ -1275,12 +1269,12 @@
         <v>58.29</v>
       </c>
       <c r="G35" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2">
         <v>45134</v>
@@ -1298,12 +1292,12 @@
         <v>57.69</v>
       </c>
       <c r="G36" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2">
         <v>45134</v>
@@ -1321,12 +1315,12 @@
         <v>57.99</v>
       </c>
       <c r="G37" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B38" s="2">
         <v>45134</v>
@@ -1344,12 +1338,12 @@
         <v>57.69</v>
       </c>
       <c r="G38" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2">
         <v>45134</v>
@@ -1367,12 +1361,12 @@
         <v>57.69</v>
       </c>
       <c r="G39" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2">
         <v>45134</v>
@@ -1390,12 +1384,12 @@
         <v>57.99</v>
       </c>
       <c r="G40" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2">
         <v>45134</v>
@@ -1413,12 +1407,12 @@
         <v>57.69</v>
       </c>
       <c r="G41" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42" s="2">
         <v>45134</v>
@@ -1436,12 +1430,12 @@
         <v>57.4</v>
       </c>
       <c r="G42" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43" s="2">
         <v>45134</v>
@@ -1459,12 +1453,12 @@
         <v>57.69</v>
       </c>
       <c r="G43" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B44" s="2">
         <v>45134</v>
@@ -1482,12 +1476,12 @@
         <v>57.4</v>
       </c>
       <c r="G44" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2">
         <v>45134</v>
@@ -1505,12 +1499,12 @@
         <v>56.82</v>
       </c>
       <c r="G45" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B46" s="2">
         <v>45134</v>
@@ -1528,12 +1522,12 @@
         <v>56.82</v>
       </c>
       <c r="G46" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2">
         <v>45134</v>
@@ -1551,12 +1545,12 @@
         <v>55.97</v>
       </c>
       <c r="G47" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" s="2">
         <v>45134</v>
@@ -1574,12 +1568,12 @@
         <v>56.25</v>
       </c>
       <c r="G48" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49" s="2">
         <v>45134</v>
@@ -1597,12 +1591,12 @@
         <v>56.53</v>
       </c>
       <c r="G49" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50" s="2">
         <v>45134</v>
@@ -1620,12 +1614,12 @@
         <v>55.69</v>
       </c>
       <c r="G50" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B51" s="2">
         <v>45134</v>
@@ -1643,12 +1637,12 @@
         <v>55.69</v>
       </c>
       <c r="G51" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B52" s="2">
         <v>45134</v>
@@ -1666,12 +1660,12 @@
         <v>55.97</v>
       </c>
       <c r="G52" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B53" s="2">
         <v>45134</v>
@@ -1689,12 +1683,12 @@
         <v>55.69</v>
       </c>
       <c r="G53" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54" s="2">
         <v>45134</v>
@@ -1712,12 +1706,12 @@
         <v>55.69</v>
       </c>
       <c r="G54" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B55" s="2">
         <v>45134</v>
@@ -1735,12 +1729,12 @@
         <v>55.15</v>
       </c>
       <c r="G55" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B56" s="2">
         <v>45134</v>
@@ -1758,12 +1752,12 @@
         <v>55.69</v>
       </c>
       <c r="G56" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B57" s="2">
         <v>45134</v>
@@ -1781,12 +1775,12 @@
         <v>54.61</v>
       </c>
       <c r="G57" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B58" s="2">
         <v>45134</v>
@@ -1804,12 +1798,12 @@
         <v>54.35</v>
       </c>
       <c r="G58" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B59" s="2">
         <v>45134</v>
@@ -1827,12 +1821,12 @@
         <v>54.88</v>
       </c>
       <c r="G59" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B60" s="2">
         <v>45134</v>
@@ -1850,12 +1844,12 @@
         <v>54.61</v>
       </c>
       <c r="G60" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61" s="2">
         <v>45134</v>
@@ -1873,12 +1867,12 @@
         <v>55.15</v>
       </c>
       <c r="G61" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" s="2">
         <v>45134</v>
@@ -1896,12 +1890,12 @@
         <v>54.35</v>
       </c>
       <c r="G62" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B63" s="2">
         <v>45134</v>
@@ -1919,12 +1913,12 @@
         <v>54.61</v>
       </c>
       <c r="G63" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B64" s="2">
         <v>45134</v>
@@ -1942,12 +1936,12 @@
         <v>54.61</v>
       </c>
       <c r="G64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B65" s="2">
         <v>45134</v>
@@ -1965,15 +1959,1488 @@
         <v>55.42</v>
       </c>
       <c r="G65" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>10</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C66">
+        <v>62.5</v>
+      </c>
+      <c r="D66">
+        <v>8.5600000000004002</v>
+      </c>
+      <c r="E66">
+        <v>8.56</v>
+      </c>
+      <c r="F66">
+        <v>26.29</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C67">
+        <v>125</v>
+      </c>
+      <c r="D67">
+        <v>13.319999999999711</v>
+      </c>
+      <c r="E67">
+        <v>4.76</v>
+      </c>
+      <c r="F67">
+        <v>47.27</v>
+      </c>
+      <c r="G67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C68">
+        <v>187.5</v>
+      </c>
+      <c r="D68">
+        <v>17.480000000000469</v>
+      </c>
+      <c r="E68">
+        <v>4.16</v>
+      </c>
+      <c r="F68">
+        <v>54.09</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C69">
+        <v>250</v>
+      </c>
+      <c r="D69">
+        <v>21.480000000000469</v>
+      </c>
+      <c r="E69">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>56.25</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+      <c r="B70" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C70">
+        <v>312.5</v>
+      </c>
+      <c r="D70">
+        <v>25.380000000000109</v>
+      </c>
+      <c r="E70">
+        <v>3.9</v>
+      </c>
+      <c r="F70">
+        <v>57.69</v>
+      </c>
+      <c r="G70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>10</v>
+      </c>
+      <c r="B71" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C71">
+        <v>375</v>
+      </c>
+      <c r="D71">
+        <v>29.199999999999822</v>
+      </c>
+      <c r="E71">
+        <v>3.82</v>
+      </c>
+      <c r="F71">
+        <v>58.9</v>
+      </c>
+      <c r="G71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>10</v>
+      </c>
+      <c r="B72" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C72">
+        <v>437.5</v>
+      </c>
+      <c r="D72">
+        <v>32.960000000000043</v>
+      </c>
+      <c r="E72">
+        <v>3.76</v>
+      </c>
+      <c r="F72">
+        <v>59.84</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C73">
+        <v>500</v>
+      </c>
+      <c r="D73">
+        <v>36.699999999999818</v>
+      </c>
+      <c r="E73">
+        <v>3.74</v>
+      </c>
+      <c r="F73">
+        <v>60.16</v>
+      </c>
+      <c r="G73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C74">
+        <v>562.5</v>
+      </c>
+      <c r="D74">
+        <v>40.420000000000073</v>
+      </c>
+      <c r="E74">
+        <v>3.72</v>
+      </c>
+      <c r="F74">
+        <v>60.48</v>
+      </c>
+      <c r="G74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C75">
+        <v>625</v>
+      </c>
+      <c r="D75">
+        <v>44.119999999999891</v>
+      </c>
+      <c r="E75">
+        <v>3.7</v>
+      </c>
+      <c r="F75">
+        <v>60.81</v>
+      </c>
+      <c r="G75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C76">
+        <v>687.5</v>
+      </c>
+      <c r="D76">
+        <v>47.840000000000153</v>
+      </c>
+      <c r="E76">
+        <v>3.72</v>
+      </c>
+      <c r="F76">
+        <v>60.48</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C77">
+        <v>750</v>
+      </c>
+      <c r="D77">
+        <v>51.539999999999957</v>
+      </c>
+      <c r="E77">
+        <v>3.7</v>
+      </c>
+      <c r="F77">
+        <v>60.81</v>
+      </c>
+      <c r="G77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C78">
+        <v>812.5</v>
+      </c>
+      <c r="D78">
+        <v>55.220000000000248</v>
+      </c>
+      <c r="E78">
+        <v>3.68</v>
+      </c>
+      <c r="F78">
+        <v>61.14</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C79">
+        <v>875</v>
+      </c>
+      <c r="D79">
+        <v>58.920000000000073</v>
+      </c>
+      <c r="E79">
+        <v>3.7</v>
+      </c>
+      <c r="F79">
+        <v>60.81</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C80">
+        <v>937.5</v>
+      </c>
+      <c r="D80">
+        <v>62.659999999999847</v>
+      </c>
+      <c r="E80">
+        <v>3.74</v>
+      </c>
+      <c r="F80">
+        <v>60.16</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C81">
+        <v>1000</v>
+      </c>
+      <c r="D81">
+        <v>66.359999999999673</v>
+      </c>
+      <c r="E81">
+        <v>3.7</v>
+      </c>
+      <c r="F81">
+        <v>60.81</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C82">
+        <v>1062.5</v>
+      </c>
+      <c r="D82">
+        <v>70.0600000000004</v>
+      </c>
+      <c r="E82">
+        <v>3.7</v>
+      </c>
+      <c r="F82">
+        <v>60.81</v>
+      </c>
+      <c r="G82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C83">
+        <v>1125</v>
+      </c>
+      <c r="D83">
+        <v>73.779999999999745</v>
+      </c>
+      <c r="E83">
+        <v>3.72</v>
+      </c>
+      <c r="F83">
+        <v>60.48</v>
+      </c>
+      <c r="G83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C84">
+        <v>1187.5</v>
+      </c>
+      <c r="D84">
+        <v>77.520000000000437</v>
+      </c>
+      <c r="E84">
+        <v>3.74</v>
+      </c>
+      <c r="F84">
+        <v>60.16</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C85">
+        <v>1250</v>
+      </c>
+      <c r="D85">
+        <v>81.260000000000218</v>
+      </c>
+      <c r="E85">
+        <v>3.74</v>
+      </c>
+      <c r="F85">
+        <v>60.16</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C86">
+        <v>1312.5</v>
+      </c>
+      <c r="D86">
+        <v>85</v>
+      </c>
+      <c r="E86">
+        <v>3.74</v>
+      </c>
+      <c r="F86">
+        <v>60.16</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C87">
+        <v>1375</v>
+      </c>
+      <c r="D87">
+        <v>88.739999999999782</v>
+      </c>
+      <c r="E87">
+        <v>3.74</v>
+      </c>
+      <c r="F87">
+        <v>60.16</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>10</v>
+      </c>
+      <c r="B88" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C88">
+        <v>1437.5</v>
+      </c>
+      <c r="D88">
+        <v>92.520000000000437</v>
+      </c>
+      <c r="E88">
+        <v>3.78</v>
+      </c>
+      <c r="F88">
+        <v>59.52</v>
+      </c>
+      <c r="G88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C89">
+        <v>1500</v>
+      </c>
+      <c r="D89">
+        <v>96.260000000000218</v>
+      </c>
+      <c r="E89">
+        <v>3.74</v>
+      </c>
+      <c r="F89">
+        <v>60.16</v>
+      </c>
+      <c r="G89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>10</v>
+      </c>
+      <c r="B90" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C90">
+        <v>1562.5</v>
+      </c>
+      <c r="D90">
+        <v>100.02000000000039</v>
+      </c>
+      <c r="E90">
+        <v>3.76</v>
+      </c>
+      <c r="F90">
+        <v>59.84</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>10</v>
+      </c>
+      <c r="B91" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C91">
+        <v>1625</v>
+      </c>
+      <c r="D91">
+        <v>103.7799999999997</v>
+      </c>
+      <c r="E91">
+        <v>3.76</v>
+      </c>
+      <c r="F91">
+        <v>59.84</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C92">
+        <v>1687.5</v>
+      </c>
+      <c r="D92">
+        <v>107.54</v>
+      </c>
+      <c r="E92">
+        <v>3.76</v>
+      </c>
+      <c r="F92">
+        <v>59.84</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>10</v>
+      </c>
+      <c r="B93" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C93">
+        <v>1750</v>
+      </c>
+      <c r="D93">
+        <v>111.31999999999969</v>
+      </c>
+      <c r="E93">
+        <v>3.78</v>
+      </c>
+      <c r="F93">
+        <v>59.52</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>10</v>
+      </c>
+      <c r="B94" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C94">
+        <v>1812.5</v>
+      </c>
+      <c r="D94">
+        <v>115.10000000000041</v>
+      </c>
+      <c r="E94">
+        <v>3.78</v>
+      </c>
+      <c r="F94">
+        <v>59.52</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>10</v>
+      </c>
+      <c r="B95" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C95">
+        <v>1875</v>
+      </c>
+      <c r="D95">
+        <v>118.8599999999997</v>
+      </c>
+      <c r="E95">
+        <v>3.76</v>
+      </c>
+      <c r="F95">
+        <v>59.84</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B96" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C96">
+        <v>1937.5</v>
+      </c>
+      <c r="D96">
+        <v>122.6599999999999</v>
+      </c>
+      <c r="E96">
+        <v>3.8</v>
+      </c>
+      <c r="F96">
+        <v>59.21</v>
+      </c>
+      <c r="G96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>10</v>
+      </c>
+      <c r="B97" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C97">
+        <v>2000</v>
+      </c>
+      <c r="D97">
+        <v>126.46</v>
+      </c>
+      <c r="E97">
+        <v>3.8</v>
+      </c>
+      <c r="F97">
+        <v>59.21</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C98">
+        <v>2062.5</v>
+      </c>
+      <c r="D98">
+        <v>130.23999999999981</v>
+      </c>
+      <c r="E98">
+        <v>3.78</v>
+      </c>
+      <c r="F98">
+        <v>59.52</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C99">
+        <v>2125</v>
+      </c>
+      <c r="D99">
+        <v>134.02000000000041</v>
+      </c>
+      <c r="E99">
+        <v>3.78</v>
+      </c>
+      <c r="F99">
+        <v>59.52</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C100">
+        <v>2187.5</v>
+      </c>
+      <c r="D100">
+        <v>137.81999999999971</v>
+      </c>
+      <c r="E100">
+        <v>3.8</v>
+      </c>
+      <c r="F100">
+        <v>59.21</v>
+      </c>
+      <c r="G100" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C101">
+        <v>2250</v>
+      </c>
+      <c r="D101">
+        <v>141.61999999999989</v>
+      </c>
+      <c r="E101">
+        <v>3.8</v>
+      </c>
+      <c r="F101">
+        <v>59.21</v>
+      </c>
+      <c r="G101" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C102">
+        <v>2312.5</v>
+      </c>
+      <c r="D102">
+        <v>145.44000000000051</v>
+      </c>
+      <c r="E102">
+        <v>3.82</v>
+      </c>
+      <c r="F102">
+        <v>58.9</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C103">
+        <v>2375</v>
+      </c>
+      <c r="D103">
+        <v>149.27999999999969</v>
+      </c>
+      <c r="E103">
+        <v>3.84</v>
+      </c>
+      <c r="F103">
+        <v>58.59</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>10</v>
+      </c>
+      <c r="B104" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C104">
+        <v>2437.5</v>
+      </c>
+      <c r="D104">
+        <v>153.11999999999989</v>
+      </c>
+      <c r="E104">
+        <v>3.84</v>
+      </c>
+      <c r="F104">
+        <v>58.59</v>
+      </c>
+      <c r="G104" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>10</v>
+      </c>
+      <c r="B105" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C105">
+        <v>2500</v>
+      </c>
+      <c r="D105">
+        <v>156.96</v>
+      </c>
+      <c r="E105">
+        <v>3.84</v>
+      </c>
+      <c r="F105">
+        <v>58.59</v>
+      </c>
+      <c r="G105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>10</v>
+      </c>
+      <c r="B106" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C106">
+        <v>2562.5</v>
+      </c>
+      <c r="D106">
+        <v>160.81999999999971</v>
+      </c>
+      <c r="E106">
+        <v>3.86</v>
+      </c>
+      <c r="F106">
+        <v>58.29</v>
+      </c>
+      <c r="G106" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>10</v>
+      </c>
+      <c r="B107" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C107">
+        <v>2625</v>
+      </c>
+      <c r="D107">
+        <v>164.68000000000029</v>
+      </c>
+      <c r="E107">
+        <v>3.86</v>
+      </c>
+      <c r="F107">
+        <v>58.29</v>
+      </c>
+      <c r="G107" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>10</v>
+      </c>
+      <c r="B108" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C108">
+        <v>2687.5</v>
+      </c>
+      <c r="D108">
+        <v>168.5799999999999</v>
+      </c>
+      <c r="E108">
+        <v>3.9</v>
+      </c>
+      <c r="F108">
+        <v>57.69</v>
+      </c>
+      <c r="G108" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>10</v>
+      </c>
+      <c r="B109" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C109">
+        <v>2750</v>
+      </c>
+      <c r="D109">
+        <v>172.44000000000051</v>
+      </c>
+      <c r="E109">
+        <v>3.86</v>
+      </c>
+      <c r="F109">
+        <v>58.29</v>
+      </c>
+      <c r="G109" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>10</v>
+      </c>
+      <c r="B110" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C110">
+        <v>2812.5</v>
+      </c>
+      <c r="D110">
+        <v>176.3599999999997</v>
+      </c>
+      <c r="E110">
+        <v>3.92</v>
+      </c>
+      <c r="F110">
+        <v>57.4</v>
+      </c>
+      <c r="G110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>10</v>
+      </c>
+      <c r="B111" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C111">
+        <v>2875</v>
+      </c>
+      <c r="D111">
+        <v>180.26000000000019</v>
+      </c>
+      <c r="E111">
+        <v>3.9</v>
+      </c>
+      <c r="F111">
+        <v>57.69</v>
+      </c>
+      <c r="G111" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>10</v>
+      </c>
+      <c r="B112" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C112">
+        <v>2937.5</v>
+      </c>
+      <c r="D112">
+        <v>184.19999999999979</v>
+      </c>
+      <c r="E112">
+        <v>3.94</v>
+      </c>
+      <c r="F112">
+        <v>57.11</v>
+      </c>
+      <c r="G112" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>10</v>
+      </c>
+      <c r="B113" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C113">
+        <v>3000</v>
+      </c>
+      <c r="D113">
+        <v>188.11999999999989</v>
+      </c>
+      <c r="E113">
+        <v>3.92</v>
+      </c>
+      <c r="F113">
+        <v>57.4</v>
+      </c>
+      <c r="G113" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>10</v>
+      </c>
+      <c r="B114" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C114">
+        <v>3062.5</v>
+      </c>
+      <c r="D114">
+        <v>192.04</v>
+      </c>
+      <c r="E114">
+        <v>3.92</v>
+      </c>
+      <c r="F114">
+        <v>57.4</v>
+      </c>
+      <c r="G114" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>10</v>
+      </c>
+      <c r="B115" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C115">
+        <v>3125</v>
+      </c>
+      <c r="D115">
+        <v>195.96</v>
+      </c>
+      <c r="E115">
+        <v>3.92</v>
+      </c>
+      <c r="F115">
+        <v>57.4</v>
+      </c>
+      <c r="G115" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>10</v>
+      </c>
+      <c r="B116" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C116">
+        <v>3187.5</v>
+      </c>
+      <c r="D116">
+        <v>199.9200000000001</v>
+      </c>
+      <c r="E116">
+        <v>3.96</v>
+      </c>
+      <c r="F116">
+        <v>56.82</v>
+      </c>
+      <c r="G116" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>10</v>
+      </c>
+      <c r="B117" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C117">
+        <v>3250</v>
+      </c>
+      <c r="D117">
+        <v>203.8599999999997</v>
+      </c>
+      <c r="E117">
+        <v>3.94</v>
+      </c>
+      <c r="F117">
+        <v>57.11</v>
+      </c>
+      <c r="G117" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>10</v>
+      </c>
+      <c r="B118" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C118">
+        <v>3312.5</v>
+      </c>
+      <c r="D118">
+        <v>207.84000000000009</v>
+      </c>
+      <c r="E118">
+        <v>3.98</v>
+      </c>
+      <c r="F118">
+        <v>56.53</v>
+      </c>
+      <c r="G118" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>10</v>
+      </c>
+      <c r="B119" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C119">
+        <v>3375</v>
+      </c>
+      <c r="D119">
+        <v>211.80000000000021</v>
+      </c>
+      <c r="E119">
+        <v>3.96</v>
+      </c>
+      <c r="F119">
+        <v>56.82</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>10</v>
+      </c>
+      <c r="B120" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C120">
+        <v>3437.5</v>
+      </c>
+      <c r="D120">
+        <v>215.80000000000021</v>
+      </c>
+      <c r="E120">
+        <v>4</v>
+      </c>
+      <c r="F120">
+        <v>56.25</v>
+      </c>
+      <c r="G120" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>10</v>
+      </c>
+      <c r="B121" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C121">
+        <v>3500</v>
+      </c>
+      <c r="D121">
+        <v>219.80000000000021</v>
+      </c>
+      <c r="E121">
+        <v>4</v>
+      </c>
+      <c r="F121">
+        <v>56.25</v>
+      </c>
+      <c r="G121" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>10</v>
+      </c>
+      <c r="B122" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C122">
+        <v>3562.5</v>
+      </c>
+      <c r="D122">
+        <v>223.80000000000021</v>
+      </c>
+      <c r="E122">
+        <v>4</v>
+      </c>
+      <c r="F122">
+        <v>56.25</v>
+      </c>
+      <c r="G122" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>10</v>
+      </c>
+      <c r="B123" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C123">
+        <v>3625</v>
+      </c>
+      <c r="D123">
+        <v>227.77999999999969</v>
+      </c>
+      <c r="E123">
+        <v>3.98</v>
+      </c>
+      <c r="F123">
+        <v>56.53</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>10</v>
+      </c>
+      <c r="B124" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C124">
+        <v>3687.5</v>
+      </c>
+      <c r="D124">
+        <v>231.80000000000021</v>
+      </c>
+      <c r="E124">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="F124">
+        <v>55.97</v>
+      </c>
+      <c r="G124" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>10</v>
+      </c>
+      <c r="B125" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C125">
+        <v>3750</v>
+      </c>
+      <c r="D125">
+        <v>235.77999999999969</v>
+      </c>
+      <c r="E125">
+        <v>3.98</v>
+      </c>
+      <c r="F125">
+        <v>56.53</v>
+      </c>
+      <c r="G125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>10</v>
+      </c>
+      <c r="B126" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C126">
+        <v>3812.5</v>
+      </c>
+      <c r="D126">
+        <v>239.77999999999969</v>
+      </c>
+      <c r="E126">
+        <v>4</v>
+      </c>
+      <c r="F126">
+        <v>56.25</v>
+      </c>
+      <c r="G126" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>10</v>
+      </c>
+      <c r="B127" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C127">
+        <v>3875</v>
+      </c>
+      <c r="D127">
+        <v>243.76000000000019</v>
+      </c>
+      <c r="E127">
+        <v>3.98</v>
+      </c>
+      <c r="F127">
+        <v>56.53</v>
+      </c>
+      <c r="G127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>10</v>
+      </c>
+      <c r="B128" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C128">
+        <v>3937.5</v>
+      </c>
+      <c r="D128">
+        <v>247.76000000000019</v>
+      </c>
+      <c r="E128">
+        <v>4</v>
+      </c>
+      <c r="F128">
+        <v>56.25</v>
+      </c>
+      <c r="G128" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>10</v>
+      </c>
+      <c r="B129" s="2">
+        <v>45144</v>
+      </c>
+      <c r="C129">
+        <v>4000</v>
+      </c>
+      <c r="D129">
+        <v>251.80000000000021</v>
+      </c>
+      <c r="E129">
+        <v>4.04</v>
+      </c>
+      <c r="F129">
+        <v>55.69</v>
+      </c>
+      <c r="G129" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J65" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J65">
-      <sortCondition descending="1" ref="B1:B65"/>
-    </sortState>
-  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/pages/video_analysis/IP_Master_Men.xlsx
+++ b/pages/video_analysis/IP_Master_Men.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26529"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9F7607-0B3F-4B96-B388-D89298914905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1008" windowWidth="11256" windowHeight="11952" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="14">
   <si>
     <t>Title</t>
   </si>
@@ -46,35 +40,32 @@
     <t>Video</t>
   </si>
   <si>
-    <t>SRM_File</t>
+    <t>23-08-06 Tom Sexton Q Glasgow WCH</t>
   </si>
   <si>
-    <t>27/7/2023 Keegan Hornblow Grenchen</t>
+    <t>23-07-27 Keegan Hornblow Grenchen</t>
   </si>
   <si>
-    <t>6/8/2023 Tom Sexton Q Glasgow WCH</t>
+    <t>geh</t>
   </si>
   <si>
     <t>No Change</t>
   </si>
   <si>
-    <t>https://youtu.be/n4bAB6UxK90</t>
+    <t>https://youtu.be/kMm4Y9rzpyc</t>
   </si>
   <si>
-    <t>Campbell_Bunch_test</t>
-  </si>
-  <si>
-    <t>https://youtu.be/kMm4Y9rzpyc</t>
+    <t>https://youtu.be/n4bAB6UxK90</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,21 +142,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -237,7 +220,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -272,10 +254,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -448,14 +429,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I129"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H193"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -480,28 +458,25 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C2">
         <v>62.5</v>
       </c>
       <c r="D2">
-        <v>8.7799999999997453</v>
+        <v>8.5600000000004</v>
       </c>
       <c r="E2">
-        <v>8.7799999999999994</v>
+        <v>8.56</v>
       </c>
       <c r="F2">
-        <v>25.63</v>
+        <v>26.29</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -509,2937 +484,4407 @@
       <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C3">
         <v>125</v>
       </c>
       <c r="D3">
-        <v>13.579999999999931</v>
+        <v>13.31999999999971</v>
       </c>
       <c r="E3">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="F3">
-        <v>46.88</v>
+        <v>47.27</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C4">
         <v>187.5</v>
       </c>
       <c r="D4">
-        <v>17.720000000000251</v>
+        <v>17.48000000000047</v>
       </c>
       <c r="E4">
-        <v>4.1399999999999997</v>
+        <v>4.16</v>
       </c>
       <c r="F4">
-        <v>54.35</v>
+        <v>54.09</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C5">
         <v>250</v>
       </c>
       <c r="D5">
-        <v>21.680000000000291</v>
+        <v>21.48000000000047</v>
       </c>
       <c r="E5">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>56.82</v>
+        <v>56.25</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C6">
         <v>312.5</v>
       </c>
       <c r="D6">
-        <v>25.5600000000004</v>
+        <v>25.38000000000011</v>
       </c>
       <c r="E6">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="F6">
-        <v>57.99</v>
+        <v>57.69</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C7">
         <v>375</v>
       </c>
       <c r="D7">
-        <v>29.39999999999964</v>
+        <v>29.19999999999982</v>
       </c>
       <c r="E7">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="F7">
-        <v>58.59</v>
+        <v>58.9</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C8">
         <v>437.5</v>
       </c>
       <c r="D8">
-        <v>33.239999999999782</v>
+        <v>32.96000000000004</v>
       </c>
       <c r="E8">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="F8">
-        <v>58.59</v>
+        <v>59.84</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C9">
         <v>500</v>
       </c>
       <c r="D9">
-        <v>37.079999999999927</v>
+        <v>36.69999999999982</v>
       </c>
       <c r="E9">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="F9">
-        <v>58.59</v>
+        <v>60.16</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C10">
         <v>562.5</v>
       </c>
       <c r="D10">
-        <v>40.920000000000073</v>
+        <v>40.42000000000007</v>
       </c>
       <c r="E10">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="F10">
-        <v>58.59</v>
+        <v>60.48</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C11">
         <v>625</v>
       </c>
       <c r="D11">
-        <v>44.720000000000248</v>
+        <v>44.11999999999989</v>
       </c>
       <c r="E11">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F11">
-        <v>59.21</v>
+        <v>60.81</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C12">
         <v>687.5</v>
       </c>
       <c r="D12">
-        <v>48.5600000000004</v>
+        <v>47.84000000000015</v>
       </c>
       <c r="E12">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="F12">
-        <v>58.59</v>
+        <v>60.48</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C13">
         <v>750</v>
       </c>
       <c r="D13">
-        <v>52.380000000000109</v>
+        <v>51.53999999999996</v>
       </c>
       <c r="E13">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="F13">
-        <v>58.9</v>
+        <v>60.81</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C14">
         <v>812.5</v>
       </c>
       <c r="D14">
-        <v>56.199999999999818</v>
+        <v>55.22000000000025</v>
       </c>
       <c r="E14">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="F14">
-        <v>58.9</v>
+        <v>61.14</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C15">
         <v>875</v>
       </c>
       <c r="D15">
-        <v>60</v>
+        <v>58.92000000000007</v>
       </c>
       <c r="E15">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F15">
-        <v>59.21</v>
+        <v>60.81</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C16">
         <v>937.5</v>
       </c>
       <c r="D16">
-        <v>63.819999999999709</v>
+        <v>62.65999999999985</v>
       </c>
       <c r="E16">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="F16">
-        <v>58.9</v>
+        <v>60.16</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C17">
         <v>1000</v>
       </c>
       <c r="D17">
-        <v>67.659999999999854</v>
+        <v>66.35999999999967</v>
       </c>
       <c r="E17">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="F17">
-        <v>58.59</v>
+        <v>60.81</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C18">
         <v>1062.5</v>
       </c>
       <c r="D18">
-        <v>71.5</v>
+        <v>70.0600000000004</v>
       </c>
       <c r="E18">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="F18">
-        <v>58.59</v>
+        <v>60.81</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C19">
         <v>1125</v>
       </c>
       <c r="D19">
-        <v>75.340000000000146</v>
+        <v>73.77999999999975</v>
       </c>
       <c r="E19">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="F19">
-        <v>58.59</v>
+        <v>60.48</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C20">
         <v>1187.5</v>
       </c>
       <c r="D20">
-        <v>79.159999999999854</v>
+        <v>77.52000000000044</v>
       </c>
       <c r="E20">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="F20">
-        <v>58.9</v>
+        <v>60.16</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C21">
         <v>1250</v>
       </c>
       <c r="D21">
-        <v>83</v>
+        <v>81.26000000000022</v>
       </c>
       <c r="E21">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="F21">
-        <v>58.59</v>
+        <v>60.16</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C22">
         <v>1312.5</v>
       </c>
       <c r="D22">
-        <v>86.819999999999709</v>
+        <v>85</v>
       </c>
       <c r="E22">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="F22">
-        <v>58.9</v>
+        <v>60.16</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C23">
         <v>1375</v>
       </c>
       <c r="D23">
-        <v>90.619999999999891</v>
+        <v>88.73999999999978</v>
       </c>
       <c r="E23">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="F23">
-        <v>59.21</v>
+        <v>60.16</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C24">
         <v>1437.5</v>
       </c>
       <c r="D24">
-        <v>94.440000000000509</v>
+        <v>92.52000000000044</v>
       </c>
       <c r="E24">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="F24">
-        <v>58.9</v>
+        <v>59.52</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C25">
         <v>1500</v>
       </c>
       <c r="D25">
-        <v>98.260000000000218</v>
+        <v>96.26000000000022</v>
       </c>
       <c r="E25">
-        <v>3.82</v>
+        <v>3.74</v>
       </c>
       <c r="F25">
-        <v>58.9</v>
+        <v>60.16</v>
       </c>
       <c r="G25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C26">
         <v>1562.5</v>
       </c>
       <c r="D26">
-        <v>102.0799999999999</v>
+        <v>100.0200000000004</v>
       </c>
       <c r="E26">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="F26">
-        <v>58.9</v>
+        <v>59.84</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C27">
         <v>1625</v>
       </c>
       <c r="D27">
-        <v>105.89999999999959</v>
+        <v>103.7799999999997</v>
       </c>
       <c r="E27">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="F27">
-        <v>58.9</v>
+        <v>59.84</v>
       </c>
       <c r="G27" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C28">
         <v>1687.5</v>
       </c>
       <c r="D28">
-        <v>109.7200000000003</v>
+        <v>107.54</v>
       </c>
       <c r="E28">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="F28">
-        <v>58.9</v>
+        <v>59.84</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C29">
         <v>1750</v>
       </c>
       <c r="D29">
-        <v>113.5799999999999</v>
+        <v>111.3199999999997</v>
       </c>
       <c r="E29">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="F29">
-        <v>58.29</v>
+        <v>59.52</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C30">
         <v>1812.5</v>
       </c>
       <c r="D30">
-        <v>117.4200000000001</v>
+        <v>115.1000000000004</v>
       </c>
       <c r="E30">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="F30">
-        <v>58.59</v>
+        <v>59.52</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C31">
         <v>1875</v>
       </c>
       <c r="D31">
-        <v>121.2600000000002</v>
+        <v>118.8599999999997</v>
       </c>
       <c r="E31">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="F31">
-        <v>58.59</v>
+        <v>59.84</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C32">
         <v>1937.5</v>
       </c>
       <c r="D32">
-        <v>125.0799999999999</v>
+        <v>122.6599999999999</v>
       </c>
       <c r="E32">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="F32">
-        <v>58.9</v>
+        <v>59.21</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C33">
         <v>2000</v>
       </c>
       <c r="D33">
-        <v>128.94000000000051</v>
+        <v>126.46</v>
       </c>
       <c r="E33">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="F33">
-        <v>58.29</v>
+        <v>59.21</v>
       </c>
       <c r="G33" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C34">
         <v>2062.5</v>
       </c>
       <c r="D34">
-        <v>132.81999999999971</v>
+        <v>130.2399999999998</v>
       </c>
       <c r="E34">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="F34">
-        <v>57.99</v>
+        <v>59.52</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C35">
         <v>2125</v>
       </c>
       <c r="D35">
-        <v>136.68000000000029</v>
+        <v>134.0200000000004</v>
       </c>
       <c r="E35">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="F35">
-        <v>58.29</v>
+        <v>59.52</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C36">
         <v>2187.5</v>
       </c>
       <c r="D36">
-        <v>140.5799999999999</v>
+        <v>137.8199999999997</v>
       </c>
       <c r="E36">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F36">
-        <v>57.69</v>
+        <v>59.21</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C37">
         <v>2250</v>
       </c>
       <c r="D37">
-        <v>144.46</v>
+        <v>141.6199999999999</v>
       </c>
       <c r="E37">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="F37">
-        <v>57.99</v>
+        <v>59.21</v>
       </c>
       <c r="G37" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B38" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C38">
         <v>2312.5</v>
       </c>
       <c r="D38">
-        <v>148.3599999999997</v>
+        <v>145.4400000000005</v>
       </c>
       <c r="E38">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="F38">
-        <v>57.69</v>
+        <v>58.9</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B39" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C39">
         <v>2375</v>
       </c>
       <c r="D39">
-        <v>152.26000000000019</v>
+        <v>149.2799999999997</v>
       </c>
       <c r="E39">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="F39">
-        <v>57.69</v>
+        <v>58.59</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B40" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C40">
         <v>2437.5</v>
       </c>
       <c r="D40">
-        <v>156.1400000000003</v>
+        <v>153.1199999999999</v>
       </c>
       <c r="E40">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="F40">
-        <v>57.99</v>
+        <v>58.59</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C41">
         <v>2500</v>
       </c>
       <c r="D41">
-        <v>160.04</v>
+        <v>156.96</v>
       </c>
       <c r="E41">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="F41">
-        <v>57.69</v>
+        <v>58.59</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B42" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C42">
         <v>2562.5</v>
       </c>
       <c r="D42">
-        <v>163.96</v>
+        <v>160.8199999999997</v>
       </c>
       <c r="E42">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="F42">
-        <v>57.4</v>
+        <v>58.29</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B43" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C43">
         <v>2625</v>
       </c>
       <c r="D43">
-        <v>167.8599999999997</v>
+        <v>164.6800000000003</v>
       </c>
       <c r="E43">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="F43">
-        <v>57.69</v>
+        <v>58.29</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C44">
         <v>2687.5</v>
       </c>
       <c r="D44">
-        <v>171.77999999999969</v>
+        <v>168.5799999999999</v>
       </c>
       <c r="E44">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="F44">
-        <v>57.4</v>
+        <v>57.69</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B45" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C45">
         <v>2750</v>
       </c>
       <c r="D45">
-        <v>175.73999999999981</v>
+        <v>172.4400000000005</v>
       </c>
       <c r="E45">
-        <v>3.96</v>
+        <v>3.86</v>
       </c>
       <c r="F45">
-        <v>56.82</v>
+        <v>58.29</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B46" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C46">
         <v>2812.5</v>
       </c>
       <c r="D46">
-        <v>179.69999999999979</v>
+        <v>176.3599999999997</v>
       </c>
       <c r="E46">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="F46">
-        <v>56.82</v>
+        <v>57.4</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B47" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C47">
         <v>2875</v>
       </c>
       <c r="D47">
-        <v>183.72000000000031</v>
+        <v>180.2600000000002</v>
       </c>
       <c r="E47">
-        <v>4.0199999999999996</v>
+        <v>3.9</v>
       </c>
       <c r="F47">
-        <v>55.97</v>
+        <v>57.69</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B48" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C48">
         <v>2937.5</v>
       </c>
       <c r="D48">
-        <v>187.72000000000031</v>
+        <v>184.1999999999998</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="F48">
-        <v>56.25</v>
+        <v>57.11</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C49">
         <v>3000</v>
       </c>
       <c r="D49">
-        <v>191.69999999999979</v>
+        <v>188.1199999999999</v>
       </c>
       <c r="E49">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="F49">
-        <v>56.53</v>
+        <v>57.4</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B50" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C50">
         <v>3062.5</v>
       </c>
       <c r="D50">
-        <v>195.73999999999981</v>
+        <v>192.04</v>
       </c>
       <c r="E50">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="F50">
-        <v>55.69</v>
+        <v>57.4</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B51" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C51">
         <v>3125</v>
       </c>
       <c r="D51">
-        <v>199.77999999999969</v>
+        <v>195.96</v>
       </c>
       <c r="E51">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="F51">
-        <v>55.69</v>
+        <v>57.4</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B52" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C52">
         <v>3187.5</v>
       </c>
       <c r="D52">
-        <v>203.80000000000021</v>
+        <v>199.9200000000001</v>
       </c>
       <c r="E52">
-        <v>4.0199999999999996</v>
+        <v>3.96</v>
       </c>
       <c r="F52">
-        <v>55.97</v>
+        <v>56.82</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C53">
         <v>3250</v>
       </c>
       <c r="D53">
-        <v>207.84000000000009</v>
+        <v>203.8599999999997</v>
       </c>
       <c r="E53">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="F53">
-        <v>55.69</v>
+        <v>57.11</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B54" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C54">
         <v>3312.5</v>
       </c>
       <c r="D54">
-        <v>211.88000000000011</v>
+        <v>207.8400000000001</v>
       </c>
       <c r="E54">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="F54">
-        <v>55.69</v>
+        <v>56.53</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B55" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C55">
         <v>3375</v>
       </c>
       <c r="D55">
-        <v>215.96</v>
+        <v>211.8000000000002</v>
       </c>
       <c r="E55">
-        <v>4.08</v>
+        <v>3.96</v>
       </c>
       <c r="F55">
-        <v>55.15</v>
+        <v>56.82</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C56">
         <v>3437.5</v>
       </c>
       <c r="D56">
-        <v>220</v>
+        <v>215.8000000000002</v>
       </c>
       <c r="E56">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="F56">
-        <v>55.69</v>
+        <v>56.25</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B57" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C57">
         <v>3500</v>
       </c>
       <c r="D57">
-        <v>224.11999999999989</v>
+        <v>219.8000000000002</v>
       </c>
       <c r="E57">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>54.61</v>
+        <v>56.25</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B58" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C58">
         <v>3562.5</v>
       </c>
       <c r="D58">
-        <v>228.26000000000019</v>
+        <v>223.8000000000002</v>
       </c>
       <c r="E58">
-        <v>4.1399999999999997</v>
+        <v>4</v>
       </c>
       <c r="F58">
-        <v>54.35</v>
+        <v>56.25</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B59" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C59">
         <v>3625</v>
       </c>
       <c r="D59">
-        <v>232.3599999999997</v>
+        <v>227.7799999999997</v>
       </c>
       <c r="E59">
-        <v>4.0999999999999996</v>
+        <v>3.98</v>
       </c>
       <c r="F59">
-        <v>54.88</v>
+        <v>56.53</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B60" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C60">
         <v>3687.5</v>
       </c>
       <c r="D60">
-        <v>236.4800000000005</v>
+        <v>231.8000000000002</v>
       </c>
       <c r="E60">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="F60">
-        <v>54.61</v>
+        <v>55.97</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B61" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C61">
         <v>3750</v>
       </c>
       <c r="D61">
-        <v>240.5600000000004</v>
+        <v>235.7799999999997</v>
       </c>
       <c r="E61">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="F61">
-        <v>55.15</v>
+        <v>56.53</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B62" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C62">
         <v>3812.5</v>
       </c>
       <c r="D62">
-        <v>244.69999999999979</v>
+        <v>239.7799999999997</v>
       </c>
       <c r="E62">
-        <v>4.1399999999999997</v>
+        <v>4</v>
       </c>
       <c r="F62">
-        <v>54.35</v>
+        <v>56.25</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B63" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C63">
         <v>3875</v>
       </c>
       <c r="D63">
-        <v>248.81999999999971</v>
+        <v>243.7600000000002</v>
       </c>
       <c r="E63">
-        <v>4.12</v>
+        <v>3.98</v>
       </c>
       <c r="F63">
-        <v>54.61</v>
+        <v>56.53</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C64">
         <v>3937.5</v>
       </c>
       <c r="D64">
-        <v>252.94000000000051</v>
+        <v>247.7600000000002</v>
       </c>
       <c r="E64">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>54.61</v>
+        <v>56.25</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B65" s="2">
-        <v>45134</v>
+        <v>45144</v>
       </c>
       <c r="C65">
         <v>4000</v>
       </c>
       <c r="D65">
-        <v>257</v>
+        <v>251.8000000000002</v>
       </c>
       <c r="E65">
-        <v>4.0599999999999996</v>
+        <v>4.04</v>
       </c>
       <c r="F65">
-        <v>55.42</v>
+        <v>55.69</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B66" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C66">
         <v>62.5</v>
       </c>
       <c r="D66">
-        <v>8.5600000000004002</v>
+        <v>8.779999999999745</v>
       </c>
       <c r="E66">
-        <v>8.56</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="F66">
-        <v>26.29</v>
+        <v>25.63</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
       </c>
-      <c r="H66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H66" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B67" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C67">
         <v>125</v>
       </c>
       <c r="D67">
-        <v>13.319999999999711</v>
+        <v>13.57999999999993</v>
       </c>
       <c r="E67">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="F67">
-        <v>47.27</v>
+        <v>46.88</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B68" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C68">
         <v>187.5</v>
       </c>
       <c r="D68">
-        <v>17.480000000000469</v>
+        <v>17.72000000000025</v>
       </c>
       <c r="E68">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="F68">
-        <v>54.09</v>
+        <v>54.35</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B69" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C69">
         <v>250</v>
       </c>
       <c r="D69">
-        <v>21.480000000000469</v>
+        <v>21.68000000000029</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="F69">
-        <v>56.25</v>
+        <v>56.82</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B70" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C70">
         <v>312.5</v>
       </c>
       <c r="D70">
-        <v>25.380000000000109</v>
+        <v>25.5600000000004</v>
       </c>
       <c r="E70">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="F70">
-        <v>57.69</v>
+        <v>57.99</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B71" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C71">
         <v>375</v>
       </c>
       <c r="D71">
-        <v>29.199999999999822</v>
+        <v>29.39999999999964</v>
       </c>
       <c r="E71">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="F71">
-        <v>58.9</v>
+        <v>58.59</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C72">
         <v>437.5</v>
       </c>
       <c r="D72">
-        <v>32.960000000000043</v>
+        <v>33.23999999999978</v>
       </c>
       <c r="E72">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="F72">
-        <v>59.84</v>
+        <v>58.59</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B73" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C73">
         <v>500</v>
       </c>
       <c r="D73">
-        <v>36.699999999999818</v>
+        <v>37.07999999999993</v>
       </c>
       <c r="E73">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="F73">
-        <v>60.16</v>
+        <v>58.59</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C74">
         <v>562.5</v>
       </c>
       <c r="D74">
-        <v>40.420000000000073</v>
+        <v>40.92000000000007</v>
       </c>
       <c r="E74">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="F74">
-        <v>60.48</v>
+        <v>58.59</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B75" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C75">
         <v>625</v>
       </c>
       <c r="D75">
-        <v>44.119999999999891</v>
+        <v>44.72000000000025</v>
       </c>
       <c r="E75">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F75">
-        <v>60.81</v>
+        <v>59.21</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B76" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C76">
         <v>687.5</v>
       </c>
       <c r="D76">
-        <v>47.840000000000153</v>
+        <v>48.5600000000004</v>
       </c>
       <c r="E76">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="F76">
-        <v>60.48</v>
+        <v>58.59</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B77" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C77">
         <v>750</v>
       </c>
       <c r="D77">
-        <v>51.539999999999957</v>
+        <v>52.38000000000011</v>
       </c>
       <c r="E77">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="F77">
-        <v>60.81</v>
+        <v>58.9</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C78">
         <v>812.5</v>
       </c>
       <c r="D78">
-        <v>55.220000000000248</v>
+        <v>56.19999999999982</v>
       </c>
       <c r="E78">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="F78">
-        <v>61.14</v>
+        <v>58.9</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B79" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C79">
         <v>875</v>
       </c>
       <c r="D79">
-        <v>58.920000000000073</v>
+        <v>60</v>
       </c>
       <c r="E79">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F79">
-        <v>60.81</v>
+        <v>59.21</v>
       </c>
       <c r="G79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B80" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C80">
         <v>937.5</v>
       </c>
       <c r="D80">
-        <v>62.659999999999847</v>
+        <v>63.81999999999971</v>
       </c>
       <c r="E80">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="F80">
-        <v>60.16</v>
+        <v>58.9</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B81" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C81">
         <v>1000</v>
       </c>
       <c r="D81">
-        <v>66.359999999999673</v>
+        <v>67.65999999999985</v>
       </c>
       <c r="E81">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="F81">
-        <v>60.81</v>
+        <v>58.59</v>
       </c>
       <c r="G81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B82" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C82">
         <v>1062.5</v>
       </c>
       <c r="D82">
-        <v>70.0600000000004</v>
+        <v>71.5</v>
       </c>
       <c r="E82">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="F82">
-        <v>60.81</v>
+        <v>58.59</v>
       </c>
       <c r="G82" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B83" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C83">
         <v>1125</v>
       </c>
       <c r="D83">
-        <v>73.779999999999745</v>
+        <v>75.34000000000015</v>
       </c>
       <c r="E83">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="F83">
-        <v>60.48</v>
+        <v>58.59</v>
       </c>
       <c r="G83" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B84" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C84">
         <v>1187.5</v>
       </c>
       <c r="D84">
-        <v>77.520000000000437</v>
+        <v>79.15999999999985</v>
       </c>
       <c r="E84">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="F84">
-        <v>60.16</v>
+        <v>58.9</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B85" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C85">
         <v>1250</v>
       </c>
       <c r="D85">
-        <v>81.260000000000218</v>
+        <v>83</v>
       </c>
       <c r="E85">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="F85">
-        <v>60.16</v>
+        <v>58.59</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B86" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C86">
         <v>1312.5</v>
       </c>
       <c r="D86">
-        <v>85</v>
+        <v>86.81999999999971</v>
       </c>
       <c r="E86">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="F86">
-        <v>60.16</v>
+        <v>58.9</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B87" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C87">
         <v>1375</v>
       </c>
       <c r="D87">
-        <v>88.739999999999782</v>
+        <v>90.61999999999989</v>
       </c>
       <c r="E87">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="F87">
-        <v>60.16</v>
+        <v>59.21</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B88" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C88">
         <v>1437.5</v>
       </c>
       <c r="D88">
-        <v>92.520000000000437</v>
+        <v>94.44000000000051</v>
       </c>
       <c r="E88">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="F88">
-        <v>59.52</v>
+        <v>58.9</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B89" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C89">
         <v>1500</v>
       </c>
       <c r="D89">
-        <v>96.260000000000218</v>
+        <v>98.26000000000022</v>
       </c>
       <c r="E89">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="F89">
-        <v>60.16</v>
+        <v>58.9</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B90" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C90">
         <v>1562.5</v>
       </c>
       <c r="D90">
-        <v>100.02000000000039</v>
+        <v>102.0799999999999</v>
       </c>
       <c r="E90">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="F90">
-        <v>59.84</v>
+        <v>58.9</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B91" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C91">
         <v>1625</v>
       </c>
       <c r="D91">
-        <v>103.7799999999997</v>
+        <v>105.8999999999996</v>
       </c>
       <c r="E91">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="F91">
-        <v>59.84</v>
+        <v>58.9</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B92" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C92">
         <v>1687.5</v>
       </c>
       <c r="D92">
-        <v>107.54</v>
+        <v>109.7200000000003</v>
       </c>
       <c r="E92">
-        <v>3.76</v>
+        <v>3.82</v>
       </c>
       <c r="F92">
-        <v>59.84</v>
+        <v>58.9</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B93" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C93">
         <v>1750</v>
       </c>
       <c r="D93">
-        <v>111.31999999999969</v>
+        <v>113.5799999999999</v>
       </c>
       <c r="E93">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="F93">
-        <v>59.52</v>
+        <v>58.29</v>
       </c>
       <c r="G93" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B94" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C94">
         <v>1812.5</v>
       </c>
       <c r="D94">
-        <v>115.10000000000041</v>
+        <v>117.4200000000001</v>
       </c>
       <c r="E94">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="F94">
-        <v>59.52</v>
+        <v>58.59</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B95" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C95">
         <v>1875</v>
       </c>
       <c r="D95">
-        <v>118.8599999999997</v>
+        <v>121.2600000000002</v>
       </c>
       <c r="E95">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="F95">
-        <v>59.84</v>
+        <v>58.59</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B96" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C96">
         <v>1937.5</v>
       </c>
       <c r="D96">
-        <v>122.6599999999999</v>
+        <v>125.0799999999999</v>
       </c>
       <c r="E96">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="F96">
-        <v>59.21</v>
+        <v>58.9</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C97">
         <v>2000</v>
       </c>
       <c r="D97">
-        <v>126.46</v>
+        <v>128.9400000000005</v>
       </c>
       <c r="E97">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="F97">
-        <v>59.21</v>
+        <v>58.29</v>
       </c>
       <c r="G97" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B98" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C98">
         <v>2062.5</v>
       </c>
       <c r="D98">
-        <v>130.23999999999981</v>
+        <v>132.8199999999997</v>
       </c>
       <c r="E98">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="F98">
-        <v>59.52</v>
+        <v>57.99</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B99" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C99">
         <v>2125</v>
       </c>
       <c r="D99">
-        <v>134.02000000000041</v>
+        <v>136.6800000000003</v>
       </c>
       <c r="E99">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="F99">
-        <v>59.52</v>
+        <v>58.29</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B100" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C100">
         <v>2187.5</v>
       </c>
       <c r="D100">
-        <v>137.81999999999971</v>
+        <v>140.5799999999999</v>
       </c>
       <c r="E100">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="F100">
-        <v>59.21</v>
+        <v>57.69</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B101" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C101">
         <v>2250</v>
       </c>
       <c r="D101">
-        <v>141.61999999999989</v>
+        <v>144.46</v>
       </c>
       <c r="E101">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="F101">
-        <v>59.21</v>
+        <v>57.99</v>
       </c>
       <c r="G101" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B102" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C102">
         <v>2312.5</v>
       </c>
       <c r="D102">
-        <v>145.44000000000051</v>
+        <v>148.3599999999997</v>
       </c>
       <c r="E102">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="F102">
-        <v>58.9</v>
+        <v>57.69</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B103" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C103">
         <v>2375</v>
       </c>
       <c r="D103">
-        <v>149.27999999999969</v>
+        <v>152.2600000000002</v>
       </c>
       <c r="E103">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="F103">
-        <v>58.59</v>
+        <v>57.69</v>
       </c>
       <c r="G103" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B104" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C104">
         <v>2437.5</v>
       </c>
       <c r="D104">
-        <v>153.11999999999989</v>
+        <v>156.1400000000003</v>
       </c>
       <c r="E104">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="F104">
-        <v>58.59</v>
+        <v>57.99</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B105" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C105">
         <v>2500</v>
       </c>
       <c r="D105">
-        <v>156.96</v>
+        <v>160.04</v>
       </c>
       <c r="E105">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="F105">
-        <v>58.59</v>
+        <v>57.69</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B106" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C106">
         <v>2562.5</v>
       </c>
       <c r="D106">
-        <v>160.81999999999971</v>
+        <v>163.96</v>
       </c>
       <c r="E106">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="F106">
-        <v>58.29</v>
+        <v>57.4</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B107" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C107">
         <v>2625</v>
       </c>
       <c r="D107">
-        <v>164.68000000000029</v>
+        <v>167.8599999999997</v>
       </c>
       <c r="E107">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="F107">
-        <v>58.29</v>
+        <v>57.69</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B108" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C108">
         <v>2687.5</v>
       </c>
       <c r="D108">
-        <v>168.5799999999999</v>
+        <v>171.7799999999997</v>
       </c>
       <c r="E108">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="F108">
-        <v>57.69</v>
+        <v>57.4</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B109" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C109">
         <v>2750</v>
       </c>
       <c r="D109">
-        <v>172.44000000000051</v>
+        <v>175.7399999999998</v>
       </c>
       <c r="E109">
-        <v>3.86</v>
+        <v>3.96</v>
       </c>
       <c r="F109">
-        <v>58.29</v>
+        <v>56.82</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B110" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C110">
         <v>2812.5</v>
       </c>
       <c r="D110">
-        <v>176.3599999999997</v>
+        <v>179.6999999999998</v>
       </c>
       <c r="E110">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="F110">
-        <v>57.4</v>
+        <v>56.82</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B111" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C111">
         <v>2875</v>
       </c>
       <c r="D111">
-        <v>180.26000000000019</v>
+        <v>183.7200000000003</v>
       </c>
       <c r="E111">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="F111">
-        <v>57.69</v>
+        <v>55.97</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B112" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C112">
         <v>2937.5</v>
       </c>
       <c r="D112">
-        <v>184.19999999999979</v>
+        <v>187.7200000000003</v>
       </c>
       <c r="E112">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="F112">
-        <v>57.11</v>
+        <v>56.25</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B113" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C113">
         <v>3000</v>
       </c>
       <c r="D113">
-        <v>188.11999999999989</v>
+        <v>191.6999999999998</v>
       </c>
       <c r="E113">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="F113">
-        <v>57.4</v>
+        <v>56.53</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B114" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C114">
         <v>3062.5</v>
       </c>
       <c r="D114">
-        <v>192.04</v>
+        <v>195.7399999999998</v>
       </c>
       <c r="E114">
-        <v>3.92</v>
+        <v>4.04</v>
       </c>
       <c r="F114">
-        <v>57.4</v>
+        <v>55.69</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B115" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C115">
         <v>3125</v>
       </c>
       <c r="D115">
-        <v>195.96</v>
+        <v>199.7799999999997</v>
       </c>
       <c r="E115">
-        <v>3.92</v>
+        <v>4.04</v>
       </c>
       <c r="F115">
-        <v>57.4</v>
+        <v>55.69</v>
       </c>
       <c r="G115" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B116" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C116">
         <v>3187.5</v>
       </c>
       <c r="D116">
-        <v>199.9200000000001</v>
+        <v>203.8000000000002</v>
       </c>
       <c r="E116">
-        <v>3.96</v>
+        <v>4.02</v>
       </c>
       <c r="F116">
-        <v>56.82</v>
+        <v>55.97</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B117" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C117">
         <v>3250</v>
       </c>
       <c r="D117">
-        <v>203.8599999999997</v>
+        <v>207.8400000000001</v>
       </c>
       <c r="E117">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="F117">
-        <v>57.11</v>
+        <v>55.69</v>
       </c>
       <c r="G117" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B118" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C118">
         <v>3312.5</v>
       </c>
       <c r="D118">
-        <v>207.84000000000009</v>
+        <v>211.8800000000001</v>
       </c>
       <c r="E118">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="F118">
-        <v>56.53</v>
+        <v>55.69</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B119" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C119">
         <v>3375</v>
       </c>
       <c r="D119">
-        <v>211.80000000000021</v>
+        <v>215.96</v>
       </c>
       <c r="E119">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="F119">
-        <v>56.82</v>
+        <v>55.15</v>
       </c>
       <c r="G119" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B120" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C120">
         <v>3437.5</v>
       </c>
       <c r="D120">
-        <v>215.80000000000021</v>
+        <v>220</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="F120">
-        <v>56.25</v>
+        <v>55.69</v>
       </c>
       <c r="G120" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B121" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C121">
         <v>3500</v>
       </c>
       <c r="D121">
-        <v>219.80000000000021</v>
+        <v>224.1199999999999</v>
       </c>
       <c r="E121">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="F121">
-        <v>56.25</v>
+        <v>54.61</v>
       </c>
       <c r="G121" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B122" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C122">
         <v>3562.5</v>
       </c>
       <c r="D122">
-        <v>223.80000000000021</v>
+        <v>228.2600000000002</v>
       </c>
       <c r="E122">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="F122">
-        <v>56.25</v>
+        <v>54.35</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B123" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C123">
         <v>3625</v>
       </c>
       <c r="D123">
-        <v>227.77999999999969</v>
+        <v>232.3599999999997</v>
       </c>
       <c r="E123">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="F123">
-        <v>56.53</v>
+        <v>54.88</v>
       </c>
       <c r="G123" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B124" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C124">
         <v>3687.5</v>
       </c>
       <c r="D124">
-        <v>231.80000000000021</v>
+        <v>236.4800000000005</v>
       </c>
       <c r="E124">
-        <v>4.0199999999999996</v>
+        <v>4.12</v>
       </c>
       <c r="F124">
-        <v>55.97</v>
+        <v>54.61</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B125" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C125">
         <v>3750</v>
       </c>
       <c r="D125">
-        <v>235.77999999999969</v>
+        <v>240.5600000000004</v>
       </c>
       <c r="E125">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="F125">
-        <v>56.53</v>
+        <v>55.15</v>
       </c>
       <c r="G125" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B126" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C126">
         <v>3812.5</v>
       </c>
       <c r="D126">
-        <v>239.77999999999969</v>
+        <v>244.6999999999998</v>
       </c>
       <c r="E126">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="F126">
-        <v>56.25</v>
+        <v>54.35</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B127" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C127">
         <v>3875</v>
       </c>
       <c r="D127">
-        <v>243.76000000000019</v>
+        <v>248.8199999999997</v>
       </c>
       <c r="E127">
-        <v>3.98</v>
+        <v>4.12</v>
       </c>
       <c r="F127">
-        <v>56.53</v>
+        <v>54.61</v>
       </c>
       <c r="G127" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B128" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C128">
         <v>3937.5</v>
       </c>
       <c r="D128">
-        <v>247.76000000000019</v>
+        <v>252.9400000000005</v>
       </c>
       <c r="E128">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="F128">
-        <v>56.25</v>
+        <v>54.61</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B129" s="2">
-        <v>45144</v>
+        <v>45134</v>
       </c>
       <c r="C129">
         <v>4000</v>
       </c>
       <c r="D129">
-        <v>251.80000000000021</v>
+        <v>257</v>
       </c>
       <c r="E129">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="F129">
-        <v>55.69</v>
+        <v>55.42</v>
       </c>
       <c r="G129" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>10</v>
+      </c>
+      <c r="B130" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C130">
+        <v>62.5</v>
+      </c>
+      <c r="D130">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="E130">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="F130">
+        <v>24.62</v>
+      </c>
+      <c r="G130" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>10</v>
+      </c>
+      <c r="B131" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C131">
+        <v>125</v>
+      </c>
+      <c r="D131">
+        <v>14.18</v>
+      </c>
+      <c r="E131">
+        <v>5.04</v>
+      </c>
+      <c r="F131">
+        <v>44.64</v>
+      </c>
+      <c r="G131" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>10</v>
+      </c>
+      <c r="B132" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C132">
+        <v>187.5</v>
+      </c>
+      <c r="D132">
+        <v>18.52</v>
+      </c>
+      <c r="E132">
+        <v>4.34</v>
+      </c>
+      <c r="F132">
+        <v>51.84</v>
+      </c>
+      <c r="G132" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>10</v>
+      </c>
+      <c r="B133" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C133">
+        <v>250</v>
+      </c>
+      <c r="D133">
+        <v>22.58</v>
+      </c>
+      <c r="E133">
+        <v>4.06</v>
+      </c>
+      <c r="F133">
+        <v>55.42</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>10</v>
+      </c>
+      <c r="B134" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C134">
+        <v>312.5</v>
+      </c>
+      <c r="D134">
+        <v>26.52</v>
+      </c>
+      <c r="E134">
+        <v>3.94</v>
+      </c>
+      <c r="F134">
+        <v>57.11</v>
+      </c>
+      <c r="G134" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>10</v>
+      </c>
+      <c r="B135" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C135">
+        <v>375</v>
+      </c>
+      <c r="D135">
+        <v>30.34</v>
+      </c>
+      <c r="E135">
+        <v>3.82</v>
+      </c>
+      <c r="F135">
+        <v>58.9</v>
+      </c>
+      <c r="G135" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>10</v>
+      </c>
+      <c r="B136" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C136">
+        <v>437.5</v>
+      </c>
+      <c r="D136">
+        <v>34.14</v>
+      </c>
+      <c r="E136">
+        <v>3.8</v>
+      </c>
+      <c r="F136">
+        <v>59.21</v>
+      </c>
+      <c r="G136" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>10</v>
+      </c>
+      <c r="B137" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C137">
+        <v>500</v>
+      </c>
+      <c r="D137">
+        <v>37.91999999999999</v>
+      </c>
+      <c r="E137">
+        <v>3.78</v>
+      </c>
+      <c r="F137">
+        <v>59.52</v>
+      </c>
+      <c r="G137" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>10</v>
+      </c>
+      <c r="B138" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C138">
+        <v>562.5</v>
+      </c>
+      <c r="D138">
+        <v>41.68</v>
+      </c>
+      <c r="E138">
+        <v>3.76</v>
+      </c>
+      <c r="F138">
+        <v>59.84</v>
+      </c>
+      <c r="G138" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>10</v>
+      </c>
+      <c r="B139" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C139">
+        <v>625</v>
+      </c>
+      <c r="D139">
+        <v>45.44</v>
+      </c>
+      <c r="E139">
+        <v>3.76</v>
+      </c>
+      <c r="F139">
+        <v>59.84</v>
+      </c>
+      <c r="G139" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>10</v>
+      </c>
+      <c r="B140" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C140">
+        <v>687.5</v>
+      </c>
+      <c r="D140">
+        <v>49.3</v>
+      </c>
+      <c r="E140">
+        <v>3.86</v>
+      </c>
+      <c r="F140">
+        <v>58.29</v>
+      </c>
+      <c r="G140" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>10</v>
+      </c>
+      <c r="B141" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C141">
+        <v>750</v>
+      </c>
+      <c r="D141">
+        <v>53.06</v>
+      </c>
+      <c r="E141">
+        <v>3.76</v>
+      </c>
+      <c r="F141">
+        <v>59.84</v>
+      </c>
+      <c r="G141" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>10</v>
+      </c>
+      <c r="B142" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C142">
+        <v>812.5</v>
+      </c>
+      <c r="D142">
+        <v>56.84</v>
+      </c>
+      <c r="E142">
+        <v>3.78</v>
+      </c>
+      <c r="F142">
+        <v>59.52</v>
+      </c>
+      <c r="G142" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>10</v>
+      </c>
+      <c r="B143" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C143">
+        <v>875</v>
+      </c>
+      <c r="D143">
+        <v>60.58</v>
+      </c>
+      <c r="E143">
+        <v>3.74</v>
+      </c>
+      <c r="F143">
+        <v>60.16</v>
+      </c>
+      <c r="G143" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>10</v>
+      </c>
+      <c r="B144" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C144">
+        <v>937.5</v>
+      </c>
+      <c r="D144">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="E144">
+        <v>3.74</v>
+      </c>
+      <c r="F144">
+        <v>60.16</v>
+      </c>
+      <c r="G144" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>10</v>
+      </c>
+      <c r="B145" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C145">
+        <v>1000</v>
+      </c>
+      <c r="D145">
+        <v>68.06</v>
+      </c>
+      <c r="E145">
+        <v>3.74</v>
+      </c>
+      <c r="F145">
+        <v>60.16</v>
+      </c>
+      <c r="G145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>10</v>
+      </c>
+      <c r="B146" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C146">
+        <v>1062.5</v>
+      </c>
+      <c r="D146">
+        <v>72</v>
+      </c>
+      <c r="E146">
+        <v>3.94</v>
+      </c>
+      <c r="F146">
+        <v>57.11</v>
+      </c>
+      <c r="G146" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>10</v>
+      </c>
+      <c r="B147" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C147">
+        <v>1125</v>
+      </c>
+      <c r="D147">
+        <v>75.73999999999999</v>
+      </c>
+      <c r="E147">
+        <v>3.74</v>
+      </c>
+      <c r="F147">
+        <v>60.16</v>
+      </c>
+      <c r="G147" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>10</v>
+      </c>
+      <c r="B148" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C148">
+        <v>1187.5</v>
+      </c>
+      <c r="D148">
+        <v>79.53999999999999</v>
+      </c>
+      <c r="E148">
+        <v>3.8</v>
+      </c>
+      <c r="F148">
+        <v>59.21</v>
+      </c>
+      <c r="G148" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>10</v>
+      </c>
+      <c r="B149" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C149">
+        <v>1250</v>
+      </c>
+      <c r="D149">
+        <v>83.28</v>
+      </c>
+      <c r="E149">
+        <v>3.74</v>
+      </c>
+      <c r="F149">
+        <v>60.16</v>
+      </c>
+      <c r="G149" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>10</v>
+      </c>
+      <c r="B150" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C150">
+        <v>1312.5</v>
+      </c>
+      <c r="D150">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="E150">
+        <v>3.82</v>
+      </c>
+      <c r="F150">
+        <v>58.9</v>
+      </c>
+      <c r="G150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>10</v>
+      </c>
+      <c r="B151" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C151">
+        <v>1375</v>
+      </c>
+      <c r="D151">
+        <v>90.86</v>
+      </c>
+      <c r="E151">
+        <v>3.76</v>
+      </c>
+      <c r="F151">
+        <v>59.84</v>
+      </c>
+      <c r="G151" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>10</v>
+      </c>
+      <c r="B152" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C152">
+        <v>1437.5</v>
+      </c>
+      <c r="D152">
+        <v>94.66</v>
+      </c>
+      <c r="E152">
+        <v>3.8</v>
+      </c>
+      <c r="F152">
+        <v>59.21</v>
+      </c>
+      <c r="G152" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>10</v>
+      </c>
+      <c r="B153" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C153">
+        <v>1500</v>
+      </c>
+      <c r="D153">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="E153">
+        <v>3.8</v>
+      </c>
+      <c r="F153">
+        <v>59.21</v>
+      </c>
+      <c r="G153" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>10</v>
+      </c>
+      <c r="B154" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C154">
+        <v>1562.5</v>
+      </c>
+      <c r="D154">
+        <v>102.22</v>
+      </c>
+      <c r="E154">
+        <v>3.76</v>
+      </c>
+      <c r="F154">
+        <v>59.84</v>
+      </c>
+      <c r="G154" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>10</v>
+      </c>
+      <c r="B155" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C155">
+        <v>1625</v>
+      </c>
+      <c r="D155">
+        <v>106</v>
+      </c>
+      <c r="E155">
+        <v>3.78</v>
+      </c>
+      <c r="F155">
+        <v>59.52</v>
+      </c>
+      <c r="G155" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>10</v>
+      </c>
+      <c r="B156" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C156">
+        <v>1687.5</v>
+      </c>
+      <c r="D156">
+        <v>109.78</v>
+      </c>
+      <c r="E156">
+        <v>3.78</v>
+      </c>
+      <c r="F156">
+        <v>59.52</v>
+      </c>
+      <c r="G156" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>10</v>
+      </c>
+      <c r="B157" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C157">
+        <v>1750</v>
+      </c>
+      <c r="D157">
+        <v>113.56</v>
+      </c>
+      <c r="E157">
+        <v>3.78</v>
+      </c>
+      <c r="F157">
+        <v>59.52</v>
+      </c>
+      <c r="G157" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>10</v>
+      </c>
+      <c r="B158" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C158">
+        <v>1812.5</v>
+      </c>
+      <c r="D158">
+        <v>117.36</v>
+      </c>
+      <c r="E158">
+        <v>3.8</v>
+      </c>
+      <c r="F158">
+        <v>59.21</v>
+      </c>
+      <c r="G158" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>10</v>
+      </c>
+      <c r="B159" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C159">
+        <v>1875</v>
+      </c>
+      <c r="D159">
+        <v>121.14</v>
+      </c>
+      <c r="E159">
+        <v>3.78</v>
+      </c>
+      <c r="F159">
+        <v>59.52</v>
+      </c>
+      <c r="G159" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C160">
+        <v>1937.5</v>
+      </c>
+      <c r="D160">
+        <v>124.96</v>
+      </c>
+      <c r="E160">
+        <v>3.82</v>
+      </c>
+      <c r="F160">
+        <v>58.9</v>
+      </c>
+      <c r="G160" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>10</v>
+      </c>
+      <c r="B161" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C161">
+        <v>2000</v>
+      </c>
+      <c r="D161">
+        <v>128.78</v>
+      </c>
+      <c r="E161">
+        <v>3.82</v>
+      </c>
+      <c r="F161">
+        <v>58.9</v>
+      </c>
+      <c r="G161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>10</v>
+      </c>
+      <c r="B162" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C162">
+        <v>2062.5</v>
+      </c>
+      <c r="D162">
+        <v>132.76</v>
+      </c>
+      <c r="E162">
+        <v>3.98</v>
+      </c>
+      <c r="F162">
+        <v>56.53</v>
+      </c>
+      <c r="G162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>10</v>
+      </c>
+      <c r="B163" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C163">
+        <v>2125</v>
+      </c>
+      <c r="D163">
+        <v>136.56</v>
+      </c>
+      <c r="E163">
+        <v>3.8</v>
+      </c>
+      <c r="F163">
+        <v>59.21</v>
+      </c>
+      <c r="G163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>10</v>
+      </c>
+      <c r="B164" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C164">
+        <v>2187.5</v>
+      </c>
+      <c r="D164">
+        <v>140.4</v>
+      </c>
+      <c r="E164">
+        <v>3.84</v>
+      </c>
+      <c r="F164">
+        <v>58.59</v>
+      </c>
+      <c r="G164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>10</v>
+      </c>
+      <c r="B165" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C165">
+        <v>2250</v>
+      </c>
+      <c r="D165">
+        <v>144.2</v>
+      </c>
+      <c r="E165">
+        <v>3.8</v>
+      </c>
+      <c r="F165">
+        <v>59.21</v>
+      </c>
+      <c r="G165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C166">
+        <v>2312.5</v>
+      </c>
+      <c r="D166">
+        <v>148.02</v>
+      </c>
+      <c r="E166">
+        <v>3.82</v>
+      </c>
+      <c r="F166">
+        <v>58.9</v>
+      </c>
+      <c r="G166" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C167">
+        <v>2375</v>
+      </c>
+      <c r="D167">
+        <v>151.8</v>
+      </c>
+      <c r="E167">
+        <v>3.78</v>
+      </c>
+      <c r="F167">
+        <v>59.52</v>
+      </c>
+      <c r="G167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C168">
+        <v>2437.5</v>
+      </c>
+      <c r="D168">
+        <v>155.56</v>
+      </c>
+      <c r="E168">
+        <v>3.76</v>
+      </c>
+      <c r="F168">
+        <v>59.84</v>
+      </c>
+      <c r="G168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>10</v>
+      </c>
+      <c r="B169" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C169">
+        <v>2500</v>
+      </c>
+      <c r="D169">
+        <v>159.3</v>
+      </c>
+      <c r="E169">
+        <v>3.74</v>
+      </c>
+      <c r="F169">
+        <v>60.16</v>
+      </c>
+      <c r="G169" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>10</v>
+      </c>
+      <c r="B170" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C170">
+        <v>2562.5</v>
+      </c>
+      <c r="D170">
+        <v>163.16</v>
+      </c>
+      <c r="E170">
+        <v>3.86</v>
+      </c>
+      <c r="F170">
+        <v>58.29</v>
+      </c>
+      <c r="G170" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>10</v>
+      </c>
+      <c r="B171" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C171">
+        <v>2625</v>
+      </c>
+      <c r="D171">
+        <v>166.9</v>
+      </c>
+      <c r="E171">
+        <v>3.74</v>
+      </c>
+      <c r="F171">
+        <v>60.16</v>
+      </c>
+      <c r="G171" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>10</v>
+      </c>
+      <c r="B172" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C172">
+        <v>2687.5</v>
+      </c>
+      <c r="D172">
+        <v>170.66</v>
+      </c>
+      <c r="E172">
+        <v>3.76</v>
+      </c>
+      <c r="F172">
+        <v>59.84</v>
+      </c>
+      <c r="G172" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>10</v>
+      </c>
+      <c r="B173" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C173">
+        <v>2750</v>
+      </c>
+      <c r="D173">
+        <v>174.44</v>
+      </c>
+      <c r="E173">
+        <v>3.78</v>
+      </c>
+      <c r="F173">
+        <v>59.52</v>
+      </c>
+      <c r="G173" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>10</v>
+      </c>
+      <c r="B174" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C174">
+        <v>2812.5</v>
+      </c>
+      <c r="D174">
+        <v>178.36</v>
+      </c>
+      <c r="E174">
+        <v>3.92</v>
+      </c>
+      <c r="F174">
+        <v>57.4</v>
+      </c>
+      <c r="G174" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>10</v>
+      </c>
+      <c r="B175" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C175">
+        <v>2875</v>
+      </c>
+      <c r="D175">
+        <v>182.12</v>
+      </c>
+      <c r="E175">
+        <v>3.76</v>
+      </c>
+      <c r="F175">
+        <v>59.84</v>
+      </c>
+      <c r="G175" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>10</v>
+      </c>
+      <c r="B176" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C176">
+        <v>2937.5</v>
+      </c>
+      <c r="D176">
+        <v>185.9</v>
+      </c>
+      <c r="E176">
+        <v>3.78</v>
+      </c>
+      <c r="F176">
+        <v>59.52</v>
+      </c>
+      <c r="G176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>10</v>
+      </c>
+      <c r="B177" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C177">
+        <v>3000</v>
+      </c>
+      <c r="D177">
+        <v>189.68</v>
+      </c>
+      <c r="E177">
+        <v>3.78</v>
+      </c>
+      <c r="F177">
+        <v>59.52</v>
+      </c>
+      <c r="G177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>10</v>
+      </c>
+      <c r="B178" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C178">
+        <v>3062.5</v>
+      </c>
+      <c r="D178">
+        <v>193.5</v>
+      </c>
+      <c r="E178">
+        <v>3.82</v>
+      </c>
+      <c r="F178">
+        <v>58.9</v>
+      </c>
+      <c r="G178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>10</v>
+      </c>
+      <c r="B179" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C179">
+        <v>3125</v>
+      </c>
+      <c r="D179">
+        <v>197.3</v>
+      </c>
+      <c r="E179">
+        <v>3.8</v>
+      </c>
+      <c r="F179">
+        <v>59.21</v>
+      </c>
+      <c r="G179" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>10</v>
+      </c>
+      <c r="B180" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C180">
+        <v>3187.5</v>
+      </c>
+      <c r="D180">
+        <v>201.28</v>
+      </c>
+      <c r="E180">
+        <v>3.98</v>
+      </c>
+      <c r="F180">
+        <v>56.53</v>
+      </c>
+      <c r="G180" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>10</v>
+      </c>
+      <c r="B181" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C181">
+        <v>3250</v>
+      </c>
+      <c r="D181">
+        <v>205.14</v>
+      </c>
+      <c r="E181">
+        <v>3.86</v>
+      </c>
+      <c r="F181">
+        <v>58.29</v>
+      </c>
+      <c r="G181" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>10</v>
+      </c>
+      <c r="B182" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C182">
+        <v>3312.5</v>
+      </c>
+      <c r="D182">
+        <v>209.02</v>
+      </c>
+      <c r="E182">
+        <v>3.88</v>
+      </c>
+      <c r="F182">
+        <v>57.99</v>
+      </c>
+      <c r="G182" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>10</v>
+      </c>
+      <c r="B183" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C183">
+        <v>3375</v>
+      </c>
+      <c r="D183">
+        <v>212.86</v>
+      </c>
+      <c r="E183">
+        <v>3.84</v>
+      </c>
+      <c r="F183">
+        <v>58.59</v>
+      </c>
+      <c r="G183" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C184">
+        <v>3437.5</v>
+      </c>
+      <c r="D184">
+        <v>216.68</v>
+      </c>
+      <c r="E184">
+        <v>3.82</v>
+      </c>
+      <c r="F184">
+        <v>58.9</v>
+      </c>
+      <c r="G184" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>10</v>
+      </c>
+      <c r="B185" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C185">
+        <v>3500</v>
+      </c>
+      <c r="D185">
+        <v>220.54</v>
+      </c>
+      <c r="E185">
+        <v>3.86</v>
+      </c>
+      <c r="F185">
+        <v>58.29</v>
+      </c>
+      <c r="G185" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>10</v>
+      </c>
+      <c r="B186" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C186">
+        <v>3562.5</v>
+      </c>
+      <c r="D186">
+        <v>224.4</v>
+      </c>
+      <c r="E186">
+        <v>3.86</v>
+      </c>
+      <c r="F186">
+        <v>58.29</v>
+      </c>
+      <c r="G186" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>10</v>
+      </c>
+      <c r="B187" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C187">
+        <v>3625</v>
+      </c>
+      <c r="D187">
+        <v>228.24</v>
+      </c>
+      <c r="E187">
+        <v>3.84</v>
+      </c>
+      <c r="F187">
+        <v>58.59</v>
+      </c>
+      <c r="G187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>10</v>
+      </c>
+      <c r="B188" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C188">
+        <v>3687.5</v>
+      </c>
+      <c r="D188">
+        <v>232.08</v>
+      </c>
+      <c r="E188">
+        <v>3.84</v>
+      </c>
+      <c r="F188">
+        <v>58.59</v>
+      </c>
+      <c r="G188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>10</v>
+      </c>
+      <c r="B189" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C189">
+        <v>3750</v>
+      </c>
+      <c r="D189">
+        <v>235.96</v>
+      </c>
+      <c r="E189">
+        <v>3.88</v>
+      </c>
+      <c r="F189">
+        <v>57.99</v>
+      </c>
+      <c r="G189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>10</v>
+      </c>
+      <c r="B190" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C190">
+        <v>3812.5</v>
+      </c>
+      <c r="D190">
+        <v>239.9</v>
+      </c>
+      <c r="E190">
+        <v>3.94</v>
+      </c>
+      <c r="F190">
+        <v>57.11</v>
+      </c>
+      <c r="G190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>10</v>
+      </c>
+      <c r="B191" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C191">
+        <v>3875</v>
+      </c>
+      <c r="D191">
+        <v>243.84</v>
+      </c>
+      <c r="E191">
+        <v>3.94</v>
+      </c>
+      <c r="F191">
+        <v>57.11</v>
+      </c>
+      <c r="G191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>10</v>
+      </c>
+      <c r="B192" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C192">
+        <v>3937.5</v>
+      </c>
+      <c r="D192">
+        <v>247.92</v>
+      </c>
+      <c r="E192">
+        <v>4.08</v>
+      </c>
+      <c r="F192">
+        <v>55.15</v>
+      </c>
+      <c r="G192" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>10</v>
+      </c>
+      <c r="B193" s="2">
+        <v>45686</v>
+      </c>
+      <c r="C193">
+        <v>4000</v>
+      </c>
+      <c r="D193">
+        <v>251.9</v>
+      </c>
+      <c r="E193">
+        <v>3.98</v>
+      </c>
+      <c r="F193">
+        <v>56.53</v>
+      </c>
+      <c r="G193" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H66" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/video_analysis/IP_Master_Men.xlsx
+++ b/pages/video_analysis/IP_Master_Men.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\video_analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A920764-F3DD-4D75-A135-4C014F9A82F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F1FC6792D89E629903ED24B2C9460C765188C8B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D1CB14-47C1-4953-96E7-B64BD2730C23}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="17">
   <si>
     <t>Title</t>
   </si>
@@ -46,50 +46,44 @@
     <t>Video</t>
   </si>
   <si>
+    <t>23-07-27 Keegan Hornblow Grenchen</t>
+  </si>
+  <si>
     <t>No Change</t>
   </si>
   <si>
     <t>https://youtu.be/n4bAB6UxK90</t>
   </si>
   <si>
+    <t>23-08-06 Tom Sexton Q Glasgow WCH</t>
+  </si>
+  <si>
     <t>https://youtu.be/kMm4Y9rzpyc</t>
   </si>
   <si>
-    <t>23-07-27 Keegan Hornblow Grenchen</t>
+    <t>26-07-31 Glasgow CWG Erwood Q</t>
   </si>
   <si>
-    <t>23-08-06 Tom Sexton Q Glasgow WCH</t>
+    <t>26-07-31 Glasgow CWG Sexton Q</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>26-07-31 Glasgow CWG Morton Q</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -100,7 +94,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -108,43 +102,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -443,50 +412,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H129"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I321"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.73046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2">
+        <v>8</v>
+      </c>
+      <c r="B2">
         <v>45134</v>
       </c>
       <c r="C2">
@@ -502,17 +464,17 @@
         <v>25.63</v>
       </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>45134</v>
       </c>
       <c r="C3">
@@ -528,14 +490,14 @@
         <v>46.88</v>
       </c>
       <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>45134</v>
       </c>
       <c r="C4">
@@ -551,14 +513,14 @@
         <v>54.35</v>
       </c>
       <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>45134</v>
       </c>
       <c r="C5">
@@ -574,14 +536,14 @@
         <v>56.82</v>
       </c>
       <c r="G5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>45134</v>
       </c>
       <c r="C6">
@@ -597,14 +559,14 @@
         <v>57.99</v>
       </c>
       <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>45134</v>
       </c>
       <c r="C7">
@@ -620,14 +582,14 @@
         <v>58.59</v>
       </c>
       <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>45134</v>
       </c>
       <c r="C8">
@@ -643,14 +605,14 @@
         <v>58.59</v>
       </c>
       <c r="G8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>45134</v>
       </c>
       <c r="C9">
@@ -666,14 +628,14 @@
         <v>58.59</v>
       </c>
       <c r="G9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>45134</v>
       </c>
       <c r="C10">
@@ -689,14 +651,14 @@
         <v>58.59</v>
       </c>
       <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>45134</v>
       </c>
       <c r="C11">
@@ -712,14 +674,14 @@
         <v>59.21</v>
       </c>
       <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>45134</v>
       </c>
       <c r="C12">
@@ -735,14 +697,14 @@
         <v>58.59</v>
       </c>
       <c r="G12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>45134</v>
       </c>
       <c r="C13">
@@ -758,14 +720,14 @@
         <v>58.9</v>
       </c>
       <c r="G13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>45134</v>
       </c>
       <c r="C14">
@@ -781,14 +743,14 @@
         <v>58.9</v>
       </c>
       <c r="G14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>45134</v>
       </c>
       <c r="C15">
@@ -804,14 +766,14 @@
         <v>59.21</v>
       </c>
       <c r="G15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>45134</v>
       </c>
       <c r="C16">
@@ -827,14 +789,14 @@
         <v>58.9</v>
       </c>
       <c r="G16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>45134</v>
       </c>
       <c r="C17">
@@ -850,14 +812,14 @@
         <v>58.59</v>
       </c>
       <c r="G17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>45134</v>
       </c>
       <c r="C18">
@@ -873,14 +835,14 @@
         <v>58.59</v>
       </c>
       <c r="G18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="B19">
         <v>45134</v>
       </c>
       <c r="C19">
@@ -896,14 +858,14 @@
         <v>58.59</v>
       </c>
       <c r="G19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>45134</v>
       </c>
       <c r="C20">
@@ -919,14 +881,14 @@
         <v>58.9</v>
       </c>
       <c r="G20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>45134</v>
       </c>
       <c r="C21">
@@ -942,14 +904,14 @@
         <v>58.59</v>
       </c>
       <c r="G21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>45134</v>
       </c>
       <c r="C22">
@@ -965,14 +927,14 @@
         <v>58.9</v>
       </c>
       <c r="G22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>45134</v>
       </c>
       <c r="C23">
@@ -988,14 +950,14 @@
         <v>59.21</v>
       </c>
       <c r="G23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>45134</v>
       </c>
       <c r="C24">
@@ -1011,14 +973,14 @@
         <v>58.9</v>
       </c>
       <c r="G24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="2">
+      <c r="B25">
         <v>45134</v>
       </c>
       <c r="C25">
@@ -1034,14 +996,14 @@
         <v>58.9</v>
       </c>
       <c r="G25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>45134</v>
       </c>
       <c r="C26">
@@ -1057,14 +1019,14 @@
         <v>58.9</v>
       </c>
       <c r="G26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>45134</v>
       </c>
       <c r="C27">
@@ -1080,14 +1042,14 @@
         <v>58.9</v>
       </c>
       <c r="G27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="2">
+      <c r="B28">
         <v>45134</v>
       </c>
       <c r="C28">
@@ -1103,14 +1065,14 @@
         <v>58.9</v>
       </c>
       <c r="G28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="2">
+      <c r="B29">
         <v>45134</v>
       </c>
       <c r="C29">
@@ -1126,14 +1088,14 @@
         <v>58.29</v>
       </c>
       <c r="G29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="2">
+      <c r="B30">
         <v>45134</v>
       </c>
       <c r="C30">
@@ -1149,14 +1111,14 @@
         <v>58.59</v>
       </c>
       <c r="G30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="2">
+      <c r="B31">
         <v>45134</v>
       </c>
       <c r="C31">
@@ -1172,14 +1134,14 @@
         <v>58.59</v>
       </c>
       <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" s="2">
+      <c r="B32">
         <v>45134</v>
       </c>
       <c r="C32">
@@ -1195,14 +1157,14 @@
         <v>58.9</v>
       </c>
       <c r="G32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" s="2">
+      <c r="B33">
         <v>45134</v>
       </c>
       <c r="C33">
@@ -1218,14 +1180,14 @@
         <v>58.29</v>
       </c>
       <c r="G33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" s="2">
+      <c r="B34">
         <v>45134</v>
       </c>
       <c r="C34">
@@ -1241,14 +1203,14 @@
         <v>57.99</v>
       </c>
       <c r="G34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="2">
+      <c r="B35">
         <v>45134</v>
       </c>
       <c r="C35">
@@ -1264,14 +1226,14 @@
         <v>58.29</v>
       </c>
       <c r="G35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" s="2">
+      <c r="B36">
         <v>45134</v>
       </c>
       <c r="C36">
@@ -1287,14 +1249,14 @@
         <v>57.69</v>
       </c>
       <c r="G36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="2">
+      <c r="B37">
         <v>45134</v>
       </c>
       <c r="C37">
@@ -1310,14 +1272,14 @@
         <v>57.99</v>
       </c>
       <c r="G37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="2">
+      <c r="B38">
         <v>45134</v>
       </c>
       <c r="C38">
@@ -1333,14 +1295,14 @@
         <v>57.69</v>
       </c>
       <c r="G38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="2">
+      <c r="B39">
         <v>45134</v>
       </c>
       <c r="C39">
@@ -1356,14 +1318,14 @@
         <v>57.69</v>
       </c>
       <c r="G39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" s="2">
+      <c r="B40">
         <v>45134</v>
       </c>
       <c r="C40">
@@ -1379,14 +1341,14 @@
         <v>57.99</v>
       </c>
       <c r="G40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="2">
+      <c r="B41">
         <v>45134</v>
       </c>
       <c r="C41">
@@ -1402,14 +1364,14 @@
         <v>57.69</v>
       </c>
       <c r="G41" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" s="2">
+      <c r="B42">
         <v>45134</v>
       </c>
       <c r="C42">
@@ -1425,14 +1387,14 @@
         <v>57.4</v>
       </c>
       <c r="G42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" s="2">
+      <c r="B43">
         <v>45134</v>
       </c>
       <c r="C43">
@@ -1448,14 +1410,14 @@
         <v>57.69</v>
       </c>
       <c r="G43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="2">
+      <c r="B44">
         <v>45134</v>
       </c>
       <c r="C44">
@@ -1471,14 +1433,14 @@
         <v>57.4</v>
       </c>
       <c r="G44" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="2">
+      <c r="B45">
         <v>45134</v>
       </c>
       <c r="C45">
@@ -1494,14 +1456,14 @@
         <v>56.82</v>
       </c>
       <c r="G45" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="2">
+      <c r="B46">
         <v>45134</v>
       </c>
       <c r="C46">
@@ -1517,14 +1479,14 @@
         <v>56.82</v>
       </c>
       <c r="G46" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" s="2">
+      <c r="B47">
         <v>45134</v>
       </c>
       <c r="C47">
@@ -1540,14 +1502,14 @@
         <v>55.97</v>
       </c>
       <c r="G47" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" s="2">
+      <c r="B48">
         <v>45134</v>
       </c>
       <c r="C48">
@@ -1563,14 +1525,14 @@
         <v>56.25</v>
       </c>
       <c r="G48" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" s="2">
+      <c r="B49">
         <v>45134</v>
       </c>
       <c r="C49">
@@ -1586,14 +1548,14 @@
         <v>56.53</v>
       </c>
       <c r="G49" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="2">
+      <c r="B50">
         <v>45134</v>
       </c>
       <c r="C50">
@@ -1609,14 +1571,14 @@
         <v>55.69</v>
       </c>
       <c r="G50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>11</v>
-      </c>
-      <c r="B51" s="2">
+      <c r="B51">
         <v>45134</v>
       </c>
       <c r="C51">
@@ -1632,14 +1594,14 @@
         <v>55.69</v>
       </c>
       <c r="G51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" s="2">
+      <c r="B52">
         <v>45134</v>
       </c>
       <c r="C52">
@@ -1655,14 +1617,14 @@
         <v>55.97</v>
       </c>
       <c r="G52" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B53" s="2">
+      <c r="B53">
         <v>45134</v>
       </c>
       <c r="C53">
@@ -1678,14 +1640,14 @@
         <v>55.69</v>
       </c>
       <c r="G53" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="2">
+      <c r="B54">
         <v>45134</v>
       </c>
       <c r="C54">
@@ -1701,14 +1663,14 @@
         <v>55.69</v>
       </c>
       <c r="G54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" s="2">
+      <c r="B55">
         <v>45134</v>
       </c>
       <c r="C55">
@@ -1724,14 +1686,14 @@
         <v>55.15</v>
       </c>
       <c r="G55" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="2">
+      <c r="B56">
         <v>45134</v>
       </c>
       <c r="C56">
@@ -1747,14 +1709,14 @@
         <v>55.69</v>
       </c>
       <c r="G56" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="2">
+      <c r="B57">
         <v>45134</v>
       </c>
       <c r="C57">
@@ -1770,14 +1732,14 @@
         <v>54.61</v>
       </c>
       <c r="G57" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" s="2">
+      <c r="B58">
         <v>45134</v>
       </c>
       <c r="C58">
@@ -1793,14 +1755,14 @@
         <v>54.35</v>
       </c>
       <c r="G58" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" s="2">
+      <c r="B59">
         <v>45134</v>
       </c>
       <c r="C59">
@@ -1816,14 +1778,14 @@
         <v>54.88</v>
       </c>
       <c r="G59" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" s="2">
+      <c r="B60">
         <v>45134</v>
       </c>
       <c r="C60">
@@ -1839,14 +1801,14 @@
         <v>54.61</v>
       </c>
       <c r="G60" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" s="2">
+      <c r="B61">
         <v>45134</v>
       </c>
       <c r="C61">
@@ -1862,14 +1824,14 @@
         <v>55.15</v>
       </c>
       <c r="G61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" s="2">
+      <c r="B62">
         <v>45134</v>
       </c>
       <c r="C62">
@@ -1885,14 +1847,14 @@
         <v>54.35</v>
       </c>
       <c r="G62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="2">
+      <c r="B63">
         <v>45134</v>
       </c>
       <c r="C63">
@@ -1908,14 +1870,14 @@
         <v>54.61</v>
       </c>
       <c r="G63" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>11</v>
-      </c>
-      <c r="B64" s="2">
+      <c r="B64">
         <v>45134</v>
       </c>
       <c r="C64">
@@ -1931,14 +1893,14 @@
         <v>54.61</v>
       </c>
       <c r="G64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="2">
+      <c r="B65">
         <v>45134</v>
       </c>
       <c r="C65">
@@ -1954,14 +1916,14 @@
         <v>55.42</v>
       </c>
       <c r="G65" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>12</v>
-      </c>
-      <c r="B66" s="2">
+        <v>11</v>
+      </c>
+      <c r="B66">
         <v>45144</v>
       </c>
       <c r="C66">
@@ -1977,17 +1939,17 @@
         <v>26.29</v>
       </c>
       <c r="G66" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="2">
+        <v>11</v>
+      </c>
+      <c r="B67">
         <v>45144</v>
       </c>
       <c r="C67">
@@ -2003,14 +1965,14 @@
         <v>47.27</v>
       </c>
       <c r="G67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" s="2">
+        <v>11</v>
+      </c>
+      <c r="B68">
         <v>45144</v>
       </c>
       <c r="C68">
@@ -2026,14 +1988,14 @@
         <v>54.09</v>
       </c>
       <c r="G68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" s="2">
+        <v>11</v>
+      </c>
+      <c r="B69">
         <v>45144</v>
       </c>
       <c r="C69">
@@ -2049,14 +2011,14 @@
         <v>56.25</v>
       </c>
       <c r="G69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>12</v>
-      </c>
-      <c r="B70" s="2">
+        <v>11</v>
+      </c>
+      <c r="B70">
         <v>45144</v>
       </c>
       <c r="C70">
@@ -2072,14 +2034,14 @@
         <v>57.69</v>
       </c>
       <c r="G70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="2">
+        <v>11</v>
+      </c>
+      <c r="B71">
         <v>45144</v>
       </c>
       <c r="C71">
@@ -2095,14 +2057,14 @@
         <v>58.9</v>
       </c>
       <c r="G71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="2">
+        <v>11</v>
+      </c>
+      <c r="B72">
         <v>45144</v>
       </c>
       <c r="C72">
@@ -2118,14 +2080,14 @@
         <v>59.84</v>
       </c>
       <c r="G72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" s="2">
+        <v>11</v>
+      </c>
+      <c r="B73">
         <v>45144</v>
       </c>
       <c r="C73">
@@ -2141,14 +2103,14 @@
         <v>60.16</v>
       </c>
       <c r="G73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>12</v>
-      </c>
-      <c r="B74" s="2">
+        <v>11</v>
+      </c>
+      <c r="B74">
         <v>45144</v>
       </c>
       <c r="C74">
@@ -2164,14 +2126,14 @@
         <v>60.48</v>
       </c>
       <c r="G74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="2">
+        <v>11</v>
+      </c>
+      <c r="B75">
         <v>45144</v>
       </c>
       <c r="C75">
@@ -2187,14 +2149,14 @@
         <v>60.81</v>
       </c>
       <c r="G75" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="2">
+        <v>11</v>
+      </c>
+      <c r="B76">
         <v>45144</v>
       </c>
       <c r="C76">
@@ -2210,14 +2172,14 @@
         <v>60.48</v>
       </c>
       <c r="G76" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" s="2">
+        <v>11</v>
+      </c>
+      <c r="B77">
         <v>45144</v>
       </c>
       <c r="C77">
@@ -2233,14 +2195,14 @@
         <v>60.81</v>
       </c>
       <c r="G77" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>12</v>
-      </c>
-      <c r="B78" s="2">
+        <v>11</v>
+      </c>
+      <c r="B78">
         <v>45144</v>
       </c>
       <c r="C78">
@@ -2256,14 +2218,14 @@
         <v>61.14</v>
       </c>
       <c r="G78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>12</v>
-      </c>
-      <c r="B79" s="2">
+        <v>11</v>
+      </c>
+      <c r="B79">
         <v>45144</v>
       </c>
       <c r="C79">
@@ -2279,14 +2241,14 @@
         <v>60.81</v>
       </c>
       <c r="G79" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>12</v>
-      </c>
-      <c r="B80" s="2">
+        <v>11</v>
+      </c>
+      <c r="B80">
         <v>45144</v>
       </c>
       <c r="C80">
@@ -2302,14 +2264,14 @@
         <v>60.16</v>
       </c>
       <c r="G80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="2">
+        <v>11</v>
+      </c>
+      <c r="B81">
         <v>45144</v>
       </c>
       <c r="C81">
@@ -2325,14 +2287,14 @@
         <v>60.81</v>
       </c>
       <c r="G81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" s="2">
+        <v>11</v>
+      </c>
+      <c r="B82">
         <v>45144</v>
       </c>
       <c r="C82">
@@ -2348,14 +2310,14 @@
         <v>60.81</v>
       </c>
       <c r="G82" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>12</v>
-      </c>
-      <c r="B83" s="2">
+        <v>11</v>
+      </c>
+      <c r="B83">
         <v>45144</v>
       </c>
       <c r="C83">
@@ -2371,14 +2333,14 @@
         <v>60.48</v>
       </c>
       <c r="G83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>12</v>
-      </c>
-      <c r="B84" s="2">
+        <v>11</v>
+      </c>
+      <c r="B84">
         <v>45144</v>
       </c>
       <c r="C84">
@@ -2394,14 +2356,14 @@
         <v>60.16</v>
       </c>
       <c r="G84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>12</v>
-      </c>
-      <c r="B85" s="2">
+        <v>11</v>
+      </c>
+      <c r="B85">
         <v>45144</v>
       </c>
       <c r="C85">
@@ -2417,14 +2379,14 @@
         <v>60.16</v>
       </c>
       <c r="G85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="2">
+        <v>11</v>
+      </c>
+      <c r="B86">
         <v>45144</v>
       </c>
       <c r="C86">
@@ -2440,14 +2402,14 @@
         <v>60.16</v>
       </c>
       <c r="G86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B87" s="2">
+        <v>11</v>
+      </c>
+      <c r="B87">
         <v>45144</v>
       </c>
       <c r="C87">
@@ -2463,14 +2425,14 @@
         <v>60.16</v>
       </c>
       <c r="G87" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>12</v>
-      </c>
-      <c r="B88" s="2">
+        <v>11</v>
+      </c>
+      <c r="B88">
         <v>45144</v>
       </c>
       <c r="C88">
@@ -2486,14 +2448,14 @@
         <v>59.52</v>
       </c>
       <c r="G88" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" s="2">
+        <v>11</v>
+      </c>
+      <c r="B89">
         <v>45144</v>
       </c>
       <c r="C89">
@@ -2509,14 +2471,14 @@
         <v>60.16</v>
       </c>
       <c r="G89" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>12</v>
-      </c>
-      <c r="B90" s="2">
+        <v>11</v>
+      </c>
+      <c r="B90">
         <v>45144</v>
       </c>
       <c r="C90">
@@ -2532,14 +2494,14 @@
         <v>59.84</v>
       </c>
       <c r="G90" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="2">
+        <v>11</v>
+      </c>
+      <c r="B91">
         <v>45144</v>
       </c>
       <c r="C91">
@@ -2555,14 +2517,14 @@
         <v>59.84</v>
       </c>
       <c r="G91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>12</v>
-      </c>
-      <c r="B92" s="2">
+        <v>11</v>
+      </c>
+      <c r="B92">
         <v>45144</v>
       </c>
       <c r="C92">
@@ -2578,14 +2540,14 @@
         <v>59.84</v>
       </c>
       <c r="G92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="2">
+        <v>11</v>
+      </c>
+      <c r="B93">
         <v>45144</v>
       </c>
       <c r="C93">
@@ -2601,14 +2563,14 @@
         <v>59.52</v>
       </c>
       <c r="G93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>12</v>
-      </c>
-      <c r="B94" s="2">
+        <v>11</v>
+      </c>
+      <c r="B94">
         <v>45144</v>
       </c>
       <c r="C94">
@@ -2624,14 +2586,14 @@
         <v>59.52</v>
       </c>
       <c r="G94" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>12</v>
-      </c>
-      <c r="B95" s="2">
+        <v>11</v>
+      </c>
+      <c r="B95">
         <v>45144</v>
       </c>
       <c r="C95">
@@ -2647,14 +2609,14 @@
         <v>59.84</v>
       </c>
       <c r="G95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>12</v>
-      </c>
-      <c r="B96" s="2">
+        <v>11</v>
+      </c>
+      <c r="B96">
         <v>45144</v>
       </c>
       <c r="C96">
@@ -2670,14 +2632,14 @@
         <v>59.21</v>
       </c>
       <c r="G96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>12</v>
-      </c>
-      <c r="B97" s="2">
+        <v>11</v>
+      </c>
+      <c r="B97">
         <v>45144</v>
       </c>
       <c r="C97">
@@ -2693,14 +2655,14 @@
         <v>59.21</v>
       </c>
       <c r="G97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>12</v>
-      </c>
-      <c r="B98" s="2">
+        <v>11</v>
+      </c>
+      <c r="B98">
         <v>45144</v>
       </c>
       <c r="C98">
@@ -2716,14 +2678,14 @@
         <v>59.52</v>
       </c>
       <c r="G98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>12</v>
-      </c>
-      <c r="B99" s="2">
+        <v>11</v>
+      </c>
+      <c r="B99">
         <v>45144</v>
       </c>
       <c r="C99">
@@ -2739,14 +2701,14 @@
         <v>59.52</v>
       </c>
       <c r="G99" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>12</v>
-      </c>
-      <c r="B100" s="2">
+        <v>11</v>
+      </c>
+      <c r="B100">
         <v>45144</v>
       </c>
       <c r="C100">
@@ -2762,14 +2724,14 @@
         <v>59.21</v>
       </c>
       <c r="G100" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>12</v>
-      </c>
-      <c r="B101" s="2">
+        <v>11</v>
+      </c>
+      <c r="B101">
         <v>45144</v>
       </c>
       <c r="C101">
@@ -2785,14 +2747,14 @@
         <v>59.21</v>
       </c>
       <c r="G101" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>12</v>
-      </c>
-      <c r="B102" s="2">
+        <v>11</v>
+      </c>
+      <c r="B102">
         <v>45144</v>
       </c>
       <c r="C102">
@@ -2808,14 +2770,14 @@
         <v>58.9</v>
       </c>
       <c r="G102" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>12</v>
-      </c>
-      <c r="B103" s="2">
+        <v>11</v>
+      </c>
+      <c r="B103">
         <v>45144</v>
       </c>
       <c r="C103">
@@ -2831,14 +2793,14 @@
         <v>58.59</v>
       </c>
       <c r="G103" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>12</v>
-      </c>
-      <c r="B104" s="2">
+        <v>11</v>
+      </c>
+      <c r="B104">
         <v>45144</v>
       </c>
       <c r="C104">
@@ -2854,14 +2816,14 @@
         <v>58.59</v>
       </c>
       <c r="G104" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>12</v>
-      </c>
-      <c r="B105" s="2">
+        <v>11</v>
+      </c>
+      <c r="B105">
         <v>45144</v>
       </c>
       <c r="C105">
@@ -2877,14 +2839,14 @@
         <v>58.59</v>
       </c>
       <c r="G105" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>12</v>
-      </c>
-      <c r="B106" s="2">
+        <v>11</v>
+      </c>
+      <c r="B106">
         <v>45144</v>
       </c>
       <c r="C106">
@@ -2900,14 +2862,14 @@
         <v>58.29</v>
       </c>
       <c r="G106" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107" s="2">
+        <v>11</v>
+      </c>
+      <c r="B107">
         <v>45144</v>
       </c>
       <c r="C107">
@@ -2923,14 +2885,14 @@
         <v>58.29</v>
       </c>
       <c r="G107" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>12</v>
-      </c>
-      <c r="B108" s="2">
+        <v>11</v>
+      </c>
+      <c r="B108">
         <v>45144</v>
       </c>
       <c r="C108">
@@ -2946,14 +2908,14 @@
         <v>57.69</v>
       </c>
       <c r="G108" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B109" s="2">
+        <v>11</v>
+      </c>
+      <c r="B109">
         <v>45144</v>
       </c>
       <c r="C109">
@@ -2969,14 +2931,14 @@
         <v>58.29</v>
       </c>
       <c r="G109" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>12</v>
-      </c>
-      <c r="B110" s="2">
+        <v>11</v>
+      </c>
+      <c r="B110">
         <v>45144</v>
       </c>
       <c r="C110">
@@ -2992,14 +2954,14 @@
         <v>57.4</v>
       </c>
       <c r="G110" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>12</v>
-      </c>
-      <c r="B111" s="2">
+        <v>11</v>
+      </c>
+      <c r="B111">
         <v>45144</v>
       </c>
       <c r="C111">
@@ -3015,14 +2977,14 @@
         <v>57.69</v>
       </c>
       <c r="G111" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>12</v>
-      </c>
-      <c r="B112" s="2">
+        <v>11</v>
+      </c>
+      <c r="B112">
         <v>45144</v>
       </c>
       <c r="C112">
@@ -3038,14 +3000,14 @@
         <v>57.11</v>
       </c>
       <c r="G112" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>12</v>
-      </c>
-      <c r="B113" s="2">
+        <v>11</v>
+      </c>
+      <c r="B113">
         <v>45144</v>
       </c>
       <c r="C113">
@@ -3061,14 +3023,14 @@
         <v>57.4</v>
       </c>
       <c r="G113" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>12</v>
-      </c>
-      <c r="B114" s="2">
+        <v>11</v>
+      </c>
+      <c r="B114">
         <v>45144</v>
       </c>
       <c r="C114">
@@ -3084,14 +3046,14 @@
         <v>57.4</v>
       </c>
       <c r="G114" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>12</v>
-      </c>
-      <c r="B115" s="2">
+        <v>11</v>
+      </c>
+      <c r="B115">
         <v>45144</v>
       </c>
       <c r="C115">
@@ -3107,14 +3069,14 @@
         <v>57.4</v>
       </c>
       <c r="G115" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>12</v>
-      </c>
-      <c r="B116" s="2">
+        <v>11</v>
+      </c>
+      <c r="B116">
         <v>45144</v>
       </c>
       <c r="C116">
@@ -3130,14 +3092,14 @@
         <v>56.82</v>
       </c>
       <c r="G116" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>12</v>
-      </c>
-      <c r="B117" s="2">
+        <v>11</v>
+      </c>
+      <c r="B117">
         <v>45144</v>
       </c>
       <c r="C117">
@@ -3153,14 +3115,14 @@
         <v>57.11</v>
       </c>
       <c r="G117" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B118" s="2">
+        <v>11</v>
+      </c>
+      <c r="B118">
         <v>45144</v>
       </c>
       <c r="C118">
@@ -3176,14 +3138,14 @@
         <v>56.53</v>
       </c>
       <c r="G118" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>12</v>
-      </c>
-      <c r="B119" s="2">
+        <v>11</v>
+      </c>
+      <c r="B119">
         <v>45144</v>
       </c>
       <c r="C119">
@@ -3199,14 +3161,14 @@
         <v>56.82</v>
       </c>
       <c r="G119" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>12</v>
-      </c>
-      <c r="B120" s="2">
+        <v>11</v>
+      </c>
+      <c r="B120">
         <v>45144</v>
       </c>
       <c r="C120">
@@ -3222,14 +3184,14 @@
         <v>56.25</v>
       </c>
       <c r="G120" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>12</v>
-      </c>
-      <c r="B121" s="2">
+        <v>11</v>
+      </c>
+      <c r="B121">
         <v>45144</v>
       </c>
       <c r="C121">
@@ -3245,14 +3207,14 @@
         <v>56.25</v>
       </c>
       <c r="G121" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>12</v>
-      </c>
-      <c r="B122" s="2">
+        <v>11</v>
+      </c>
+      <c r="B122">
         <v>45144</v>
       </c>
       <c r="C122">
@@ -3268,14 +3230,14 @@
         <v>56.25</v>
       </c>
       <c r="G122" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>12</v>
-      </c>
-      <c r="B123" s="2">
+        <v>11</v>
+      </c>
+      <c r="B123">
         <v>45144</v>
       </c>
       <c r="C123">
@@ -3291,14 +3253,14 @@
         <v>56.53</v>
       </c>
       <c r="G123" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>12</v>
-      </c>
-      <c r="B124" s="2">
+        <v>11</v>
+      </c>
+      <c r="B124">
         <v>45144</v>
       </c>
       <c r="C124">
@@ -3314,14 +3276,14 @@
         <v>55.97</v>
       </c>
       <c r="G124" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>12</v>
-      </c>
-      <c r="B125" s="2">
+        <v>11</v>
+      </c>
+      <c r="B125">
         <v>45144</v>
       </c>
       <c r="C125">
@@ -3337,14 +3299,14 @@
         <v>56.53</v>
       </c>
       <c r="G125" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>12</v>
-      </c>
-      <c r="B126" s="2">
+        <v>11</v>
+      </c>
+      <c r="B126">
         <v>45144</v>
       </c>
       <c r="C126">
@@ -3360,14 +3322,14 @@
         <v>56.25</v>
       </c>
       <c r="G126" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>12</v>
-      </c>
-      <c r="B127" s="2">
+        <v>11</v>
+      </c>
+      <c r="B127">
         <v>45144</v>
       </c>
       <c r="C127">
@@ -3383,14 +3345,14 @@
         <v>56.53</v>
       </c>
       <c r="G127" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>12</v>
-      </c>
-      <c r="B128" s="2">
+        <v>11</v>
+      </c>
+      <c r="B128">
         <v>45144</v>
       </c>
       <c r="C128">
@@ -3406,14 +3368,14 @@
         <v>56.25</v>
       </c>
       <c r="G128" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129" s="2">
+        <v>11</v>
+      </c>
+      <c r="B129">
         <v>45144</v>
       </c>
       <c r="C129">
@@ -3429,7 +3391,4231 @@
         <v>55.69</v>
       </c>
       <c r="G129" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130">
+        <v>62.5</v>
+      </c>
+      <c r="D130">
+        <v>8.9226159999999997</v>
+      </c>
+      <c r="E130">
+        <v>8.9226159999999997</v>
+      </c>
+      <c r="F130">
+        <v>25.216819820000001</v>
+      </c>
+      <c r="G130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131">
+        <v>125</v>
+      </c>
+      <c r="D131">
+        <v>13.786624</v>
+      </c>
+      <c r="E131">
+        <v>4.8640079999999983</v>
+      </c>
+      <c r="F131">
+        <v>46.258147600000001</v>
+      </c>
+      <c r="G131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132">
+        <v>187.5</v>
+      </c>
+      <c r="D132">
+        <v>17.923559000000001</v>
+      </c>
+      <c r="E132">
+        <v>4.1369350000000011</v>
+      </c>
+      <c r="F132">
+        <v>54.388091670000001</v>
+      </c>
+      <c r="G132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133">
+        <v>250</v>
+      </c>
+      <c r="D133">
+        <v>21.843554999999999</v>
+      </c>
+      <c r="E133">
+        <v>3.9199959999999976</v>
+      </c>
+      <c r="F133">
+        <v>57.398017750000001</v>
+      </c>
+      <c r="G133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>13</v>
+      </c>
+      <c r="C134">
+        <v>312.5</v>
+      </c>
+      <c r="D134">
+        <v>25.663550000000001</v>
+      </c>
+      <c r="E134">
+        <v>3.8199950000000058</v>
+      </c>
+      <c r="F134">
+        <v>58.900600660000002</v>
+      </c>
+      <c r="G134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135">
+        <v>375</v>
+      </c>
+      <c r="D135">
+        <v>29.403549000000002</v>
+      </c>
+      <c r="E135">
+        <v>3.7399989999999974</v>
+      </c>
+      <c r="F135">
+        <v>60.160443890000003</v>
+      </c>
+      <c r="G135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136">
+        <v>437.5</v>
+      </c>
+      <c r="D136">
+        <v>33.103548000000004</v>
+      </c>
+      <c r="E136">
+        <v>3.6999989999999983</v>
+      </c>
+      <c r="F136">
+        <v>60.810827250000003</v>
+      </c>
+      <c r="G136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>13</v>
+      </c>
+      <c r="C137">
+        <v>500</v>
+      </c>
+      <c r="D137">
+        <v>36.743546000000002</v>
+      </c>
+      <c r="E137">
+        <v>3.6399979999999985</v>
+      </c>
+      <c r="F137">
+        <v>61.813220780000002</v>
+      </c>
+      <c r="G137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138">
+        <v>562.5</v>
+      </c>
+      <c r="D138">
+        <v>40.403545000000001</v>
+      </c>
+      <c r="E138">
+        <v>3.6599990000000062</v>
+      </c>
+      <c r="F138">
+        <v>61.475426630000001</v>
+      </c>
+      <c r="G138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139">
+        <v>625</v>
+      </c>
+      <c r="D139">
+        <v>44.043545000000002</v>
+      </c>
+      <c r="E139">
+        <v>3.6399999999999935</v>
+      </c>
+      <c r="F139">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140">
+        <v>687.5</v>
+      </c>
+      <c r="D140">
+        <v>47.703544999999998</v>
+      </c>
+      <c r="E140">
+        <v>3.6600000000000037</v>
+      </c>
+      <c r="F140">
+        <v>61.475409839999998</v>
+      </c>
+      <c r="G140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141">
+        <v>750</v>
+      </c>
+      <c r="D141">
+        <v>51.363545000000002</v>
+      </c>
+      <c r="E141">
+        <v>3.6599999999999966</v>
+      </c>
+      <c r="F141">
+        <v>61.475409839999998</v>
+      </c>
+      <c r="G141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142">
+        <v>812.5</v>
+      </c>
+      <c r="D142">
+        <v>55.043543</v>
+      </c>
+      <c r="E142">
+        <v>3.6799979999999977</v>
+      </c>
+      <c r="F142">
+        <v>61.141337579999998</v>
+      </c>
+      <c r="G142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143">
+        <v>875</v>
+      </c>
+      <c r="D143">
+        <v>58.683543</v>
+      </c>
+      <c r="E143">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="F143">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144">
+        <v>937.5</v>
+      </c>
+      <c r="D144">
+        <v>62.343541999999999</v>
+      </c>
+      <c r="E144">
+        <v>3.6599989999999991</v>
+      </c>
+      <c r="F144">
+        <v>61.475426630000001</v>
+      </c>
+      <c r="G144" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145">
+        <v>1000</v>
+      </c>
+      <c r="D145">
+        <v>65.983541000000002</v>
+      </c>
+      <c r="E145">
+        <v>3.6399990000000031</v>
+      </c>
+      <c r="F145">
+        <v>61.813203790000003</v>
+      </c>
+      <c r="G145" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146">
+        <v>1062.5</v>
+      </c>
+      <c r="D146">
+        <v>69.623541000000003</v>
+      </c>
+      <c r="E146">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="F146">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G146" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147">
+        <v>1125</v>
+      </c>
+      <c r="D147">
+        <v>73.243540999999993</v>
+      </c>
+      <c r="E147">
+        <v>3.6200000000000045</v>
+      </c>
+      <c r="F147">
+        <v>62.154696129999998</v>
+      </c>
+      <c r="G147" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148">
+        <v>1187.5</v>
+      </c>
+      <c r="D148">
+        <v>76.883539999999996</v>
+      </c>
+      <c r="E148">
+        <v>3.6399990000000031</v>
+      </c>
+      <c r="F148">
+        <v>61.813203790000003</v>
+      </c>
+      <c r="G148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149">
+        <v>1250</v>
+      </c>
+      <c r="D149">
+        <v>80.523539999999997</v>
+      </c>
+      <c r="E149">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="F149">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G149" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150">
+        <v>1312.5</v>
+      </c>
+      <c r="D150">
+        <v>84.163539999999998</v>
+      </c>
+      <c r="E150">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="F150">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>13</v>
+      </c>
+      <c r="C151">
+        <v>1375</v>
+      </c>
+      <c r="D151">
+        <v>87.803539999999998</v>
+      </c>
+      <c r="E151">
+        <v>3.6399999999999864</v>
+      </c>
+      <c r="F151">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G151" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152">
+        <v>1437.5</v>
+      </c>
+      <c r="D152">
+        <v>91.443539999999999</v>
+      </c>
+      <c r="E152">
+        <v>3.6400000000000006</v>
+      </c>
+      <c r="F152">
+        <v>61.813186809999998</v>
+      </c>
+      <c r="G152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153">
+        <v>1500</v>
+      </c>
+      <c r="D153">
+        <v>95.103538999999998</v>
+      </c>
+      <c r="E153">
+        <v>3.6599990000000133</v>
+      </c>
+      <c r="F153">
+        <v>61.475426630000001</v>
+      </c>
+      <c r="G153" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154">
+        <v>1562.5</v>
+      </c>
+      <c r="D154">
+        <v>98.783539000000005</v>
+      </c>
+      <c r="E154">
+        <v>3.6799999999999926</v>
+      </c>
+      <c r="F154">
+        <v>61.141304349999999</v>
+      </c>
+      <c r="G154" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155">
+        <v>1625</v>
+      </c>
+      <c r="D155">
+        <v>102.463539</v>
+      </c>
+      <c r="E155">
+        <v>3.6800000000000068</v>
+      </c>
+      <c r="F155">
+        <v>61.141304349999999</v>
+      </c>
+      <c r="G155" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156">
+        <v>1687.5</v>
+      </c>
+      <c r="D156">
+        <v>106.163539</v>
+      </c>
+      <c r="E156">
+        <v>3.6999999999999886</v>
+      </c>
+      <c r="F156">
+        <v>60.81081081</v>
+      </c>
+      <c r="G156" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157">
+        <v>1750</v>
+      </c>
+      <c r="D157">
+        <v>109.84353900000001</v>
+      </c>
+      <c r="E157">
+        <v>3.6800000000000068</v>
+      </c>
+      <c r="F157">
+        <v>61.141304349999999</v>
+      </c>
+      <c r="G157" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158">
+        <v>1812.5</v>
+      </c>
+      <c r="D158">
+        <v>113.543539</v>
+      </c>
+      <c r="E158">
+        <v>3.7000000000000028</v>
+      </c>
+      <c r="F158">
+        <v>60.81081081</v>
+      </c>
+      <c r="G158" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159">
+        <v>1875</v>
+      </c>
+      <c r="D159">
+        <v>117.26353899999999</v>
+      </c>
+      <c r="E159">
+        <v>3.7199999999999989</v>
+      </c>
+      <c r="F159">
+        <v>60.483870969999998</v>
+      </c>
+      <c r="G159" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160">
+        <v>1937.5</v>
+      </c>
+      <c r="D160">
+        <v>120.98353899999999</v>
+      </c>
+      <c r="E160">
+        <v>3.7199999999999989</v>
+      </c>
+      <c r="F160">
+        <v>60.483870969999998</v>
+      </c>
+      <c r="G160" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161">
+        <v>2000</v>
+      </c>
+      <c r="D161">
+        <v>124.70353900000001</v>
+      </c>
+      <c r="E161">
+        <v>3.7199999999999989</v>
+      </c>
+      <c r="F161">
+        <v>60.483870969999998</v>
+      </c>
+      <c r="G161" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162">
+        <v>2062.5</v>
+      </c>
+      <c r="D162">
+        <v>128.463539</v>
+      </c>
+      <c r="E162">
+        <v>3.7599999999999909</v>
+      </c>
+      <c r="F162">
+        <v>59.840425529999997</v>
+      </c>
+      <c r="G162" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163">
+        <v>2125</v>
+      </c>
+      <c r="D163">
+        <v>132.20353800000001</v>
+      </c>
+      <c r="E163">
+        <v>3.7399990000000116</v>
+      </c>
+      <c r="F163">
+        <v>60.160443890000003</v>
+      </c>
+      <c r="G163" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164">
+        <v>2187.5</v>
+      </c>
+      <c r="D164">
+        <v>135.98353800000001</v>
+      </c>
+      <c r="E164">
+        <v>3.7800000000000011</v>
+      </c>
+      <c r="F164">
+        <v>59.52380952</v>
+      </c>
+      <c r="G164" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165">
+        <v>2250</v>
+      </c>
+      <c r="D165">
+        <v>139.743538</v>
+      </c>
+      <c r="E165">
+        <v>3.7599999999999909</v>
+      </c>
+      <c r="F165">
+        <v>59.840425529999997</v>
+      </c>
+      <c r="G165" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166">
+        <v>2312.5</v>
+      </c>
+      <c r="D166">
+        <v>143.523538</v>
+      </c>
+      <c r="E166">
+        <v>3.7800000000000011</v>
+      </c>
+      <c r="F166">
+        <v>59.52380952</v>
+      </c>
+      <c r="G166" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167">
+        <v>2375</v>
+      </c>
+      <c r="D167">
+        <v>147.28353799999999</v>
+      </c>
+      <c r="E167">
+        <v>3.7599999999999909</v>
+      </c>
+      <c r="F167">
+        <v>59.840425529999997</v>
+      </c>
+      <c r="G167" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168">
+        <v>2437.5</v>
+      </c>
+      <c r="D168">
+        <v>151.063537</v>
+      </c>
+      <c r="E168">
+        <v>3.7799990000000037</v>
+      </c>
+      <c r="F168">
+        <v>59.523825270000003</v>
+      </c>
+      <c r="G168" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>13</v>
+      </c>
+      <c r="C169">
+        <v>2500</v>
+      </c>
+      <c r="D169">
+        <v>154.88353699999999</v>
+      </c>
+      <c r="E169">
+        <v>3.8200000000000216</v>
+      </c>
+      <c r="F169">
+        <v>58.900523560000003</v>
+      </c>
+      <c r="G169" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170">
+        <v>2562.5</v>
+      </c>
+      <c r="D170">
+        <v>158.683537</v>
+      </c>
+      <c r="E170">
+        <v>3.7999999999999829</v>
+      </c>
+      <c r="F170">
+        <v>59.21052632</v>
+      </c>
+      <c r="G170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171">
+        <v>2625</v>
+      </c>
+      <c r="D171">
+        <v>162.48353700000001</v>
+      </c>
+      <c r="E171">
+        <v>3.8000000000000114</v>
+      </c>
+      <c r="F171">
+        <v>59.21052632</v>
+      </c>
+      <c r="G171" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172">
+        <v>2687.5</v>
+      </c>
+      <c r="D172">
+        <v>166.30353700000001</v>
+      </c>
+      <c r="E172">
+        <v>3.8199999999999932</v>
+      </c>
+      <c r="F172">
+        <v>58.900523560000003</v>
+      </c>
+      <c r="G172" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173">
+        <v>2750</v>
+      </c>
+      <c r="D173">
+        <v>170.123537</v>
+      </c>
+      <c r="E173">
+        <v>3.8199999999999932</v>
+      </c>
+      <c r="F173">
+        <v>58.900523560000003</v>
+      </c>
+      <c r="G173" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174">
+        <v>2812.5</v>
+      </c>
+      <c r="D174">
+        <v>173.963537</v>
+      </c>
+      <c r="E174">
+        <v>3.8400000000000034</v>
+      </c>
+      <c r="F174">
+        <v>58.59375</v>
+      </c>
+      <c r="G174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175">
+        <v>2875</v>
+      </c>
+      <c r="D175">
+        <v>177.80353700000001</v>
+      </c>
+      <c r="E175">
+        <v>3.8400000000000034</v>
+      </c>
+      <c r="F175">
+        <v>58.59375</v>
+      </c>
+      <c r="G175" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176">
+        <v>2937.5</v>
+      </c>
+      <c r="D176">
+        <v>181.64353700000001</v>
+      </c>
+      <c r="E176">
+        <v>3.8400000000000034</v>
+      </c>
+      <c r="F176">
+        <v>58.59375</v>
+      </c>
+      <c r="G176" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177">
+        <v>3000</v>
+      </c>
+      <c r="D177">
+        <v>185.48353700000001</v>
+      </c>
+      <c r="E177">
+        <v>3.8400000000000034</v>
+      </c>
+      <c r="F177">
+        <v>58.59375</v>
+      </c>
+      <c r="G177" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178">
+        <v>3062.5</v>
+      </c>
+      <c r="D178">
+        <v>189.32353699999999</v>
+      </c>
+      <c r="E178">
+        <v>3.8400000000000034</v>
+      </c>
+      <c r="F178">
+        <v>58.59375</v>
+      </c>
+      <c r="G178" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179">
+        <v>3125</v>
+      </c>
+      <c r="D179">
+        <v>193.183537</v>
+      </c>
+      <c r="E179">
+        <v>3.8599999999999852</v>
+      </c>
+      <c r="F179">
+        <v>58.290155439999999</v>
+      </c>
+      <c r="G179" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180">
+        <v>3187.5</v>
+      </c>
+      <c r="D180">
+        <v>197.063537</v>
+      </c>
+      <c r="E180">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F180">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G180" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>13</v>
+      </c>
+      <c r="C181">
+        <v>3250</v>
+      </c>
+      <c r="D181">
+        <v>200.92353600000001</v>
+      </c>
+      <c r="E181">
+        <v>3.8599990000000162</v>
+      </c>
+      <c r="F181">
+        <v>58.290170539999998</v>
+      </c>
+      <c r="G181" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>13</v>
+      </c>
+      <c r="C182">
+        <v>3312.5</v>
+      </c>
+      <c r="D182">
+        <v>204.82353599999999</v>
+      </c>
+      <c r="E182">
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="F182">
+        <v>57.69230769</v>
+      </c>
+      <c r="G182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>13</v>
+      </c>
+      <c r="C183">
+        <v>3375</v>
+      </c>
+      <c r="D183">
+        <v>208.70353499999999</v>
+      </c>
+      <c r="E183">
+        <v>3.879998999999998</v>
+      </c>
+      <c r="F183">
+        <v>57.989705669999999</v>
+      </c>
+      <c r="G183" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>13</v>
+      </c>
+      <c r="C184">
+        <v>3437.5</v>
+      </c>
+      <c r="D184">
+        <v>212.60353499999999</v>
+      </c>
+      <c r="E184">
+        <v>3.8999999999999773</v>
+      </c>
+      <c r="F184">
+        <v>57.69230769</v>
+      </c>
+      <c r="G184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>13</v>
+      </c>
+      <c r="C185">
+        <v>3500</v>
+      </c>
+      <c r="D185">
+        <v>216.48353399999999</v>
+      </c>
+      <c r="E185">
+        <v>3.879998999999998</v>
+      </c>
+      <c r="F185">
+        <v>57.989705669999999</v>
+      </c>
+      <c r="G185" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>13</v>
+      </c>
+      <c r="C186">
+        <v>3562.5</v>
+      </c>
+      <c r="D186">
+        <v>220.40353300000001</v>
+      </c>
+      <c r="E186">
+        <v>3.9199990000000184</v>
+      </c>
+      <c r="F186">
+        <v>57.397973829999998</v>
+      </c>
+      <c r="G186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>13</v>
+      </c>
+      <c r="C187">
+        <v>3625</v>
+      </c>
+      <c r="D187">
+        <v>224.30353199999999</v>
+      </c>
+      <c r="E187">
+        <v>3.8999990000000082</v>
+      </c>
+      <c r="F187">
+        <v>57.692322490000002</v>
+      </c>
+      <c r="G187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>13</v>
+      </c>
+      <c r="C188">
+        <v>3687.5</v>
+      </c>
+      <c r="D188">
+        <v>228.16353100000001</v>
+      </c>
+      <c r="E188">
+        <v>3.8599989999999877</v>
+      </c>
+      <c r="F188">
+        <v>58.290170539999998</v>
+      </c>
+      <c r="G188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>13</v>
+      </c>
+      <c r="C189">
+        <v>3750</v>
+      </c>
+      <c r="D189">
+        <v>232.043531</v>
+      </c>
+      <c r="E189">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F189">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>13</v>
+      </c>
+      <c r="C190">
+        <v>3812.5</v>
+      </c>
+      <c r="D190">
+        <v>235.923531</v>
+      </c>
+      <c r="E190">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F190">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191">
+        <v>3875</v>
+      </c>
+      <c r="D191">
+        <v>239.76353</v>
+      </c>
+      <c r="E191">
+        <v>3.8399990000000059</v>
+      </c>
+      <c r="F191">
+        <v>58.593765259999998</v>
+      </c>
+      <c r="G191" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>13</v>
+      </c>
+      <c r="C192">
+        <v>3937.5</v>
+      </c>
+      <c r="D192">
+        <v>243.60353000000001</v>
+      </c>
+      <c r="E192">
+        <v>3.8400000000000034</v>
+      </c>
+      <c r="F192">
+        <v>58.59375</v>
+      </c>
+      <c r="G192" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>13</v>
+      </c>
+      <c r="C193">
+        <v>4000</v>
+      </c>
+      <c r="D193">
+        <v>247.423528</v>
+      </c>
+      <c r="E193">
+        <v>3.8199979999999982</v>
+      </c>
+      <c r="F193">
+        <v>58.900554399999997</v>
+      </c>
+      <c r="G193" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>14</v>
+      </c>
+      <c r="C194">
+        <v>62.5</v>
+      </c>
+      <c r="D194">
+        <v>8.560276</v>
+      </c>
+      <c r="E194">
+        <v>8.560276</v>
+      </c>
+      <c r="F194">
+        <v>26.28419925</v>
+      </c>
+      <c r="G194" t="s">
+        <v>9</v>
+      </c>
+      <c r="I194" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>14</v>
+      </c>
+      <c r="C195">
+        <v>125</v>
+      </c>
+      <c r="D195">
+        <v>13.45153</v>
+      </c>
+      <c r="E195">
+        <v>4.891254</v>
+      </c>
+      <c r="F195">
+        <v>46.000473499999998</v>
+      </c>
+      <c r="G195" t="s">
+        <v>9</v>
+      </c>
+      <c r="I195" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>14</v>
+      </c>
+      <c r="C196">
+        <v>187.5</v>
+      </c>
+      <c r="D196">
+        <v>17.691528999999999</v>
+      </c>
+      <c r="E196">
+        <v>4.239999000000001</v>
+      </c>
+      <c r="F196">
+        <v>53.066050250000004</v>
+      </c>
+      <c r="G196" t="s">
+        <v>9</v>
+      </c>
+      <c r="I196" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>14</v>
+      </c>
+      <c r="C197">
+        <v>250</v>
+      </c>
+      <c r="D197">
+        <v>21.751529000000001</v>
+      </c>
+      <c r="E197">
+        <v>4.0599999999999987</v>
+      </c>
+      <c r="F197">
+        <v>55.418719209999999</v>
+      </c>
+      <c r="G197" t="s">
+        <v>9</v>
+      </c>
+      <c r="I197" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>14</v>
+      </c>
+      <c r="C198">
+        <v>312.5</v>
+      </c>
+      <c r="D198">
+        <v>25.691524000000001</v>
+      </c>
+      <c r="E198">
+        <v>3.9399950000000032</v>
+      </c>
+      <c r="F198">
+        <v>57.106671460000001</v>
+      </c>
+      <c r="G198" t="s">
+        <v>9</v>
+      </c>
+      <c r="I198" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>14</v>
+      </c>
+      <c r="C199">
+        <v>375</v>
+      </c>
+      <c r="D199">
+        <v>29.531521999999999</v>
+      </c>
+      <c r="E199">
+        <v>3.8399980000000014</v>
+      </c>
+      <c r="F199">
+        <v>58.593780520000003</v>
+      </c>
+      <c r="G199" t="s">
+        <v>9</v>
+      </c>
+      <c r="I199" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>14</v>
+      </c>
+      <c r="C200">
+        <v>437.5</v>
+      </c>
+      <c r="D200">
+        <v>33.331521000000002</v>
+      </c>
+      <c r="E200">
+        <v>3.7999989999999997</v>
+      </c>
+      <c r="F200">
+        <v>59.210541900000003</v>
+      </c>
+      <c r="G200" t="s">
+        <v>9</v>
+      </c>
+      <c r="I200" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>14</v>
+      </c>
+      <c r="C201">
+        <v>500</v>
+      </c>
+      <c r="D201">
+        <v>37.111521000000003</v>
+      </c>
+      <c r="E201">
+        <v>3.779999999999994</v>
+      </c>
+      <c r="F201">
+        <v>59.52380952</v>
+      </c>
+      <c r="G201" t="s">
+        <v>9</v>
+      </c>
+      <c r="I201" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202">
+        <v>562.5</v>
+      </c>
+      <c r="D202">
+        <v>40.871518000000002</v>
+      </c>
+      <c r="E202">
+        <v>3.7599970000000056</v>
+      </c>
+      <c r="F202">
+        <v>59.840473279999998</v>
+      </c>
+      <c r="G202" t="s">
+        <v>9</v>
+      </c>
+      <c r="I202" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>14</v>
+      </c>
+      <c r="C203">
+        <v>625</v>
+      </c>
+      <c r="D203">
+        <v>44.651518000000003</v>
+      </c>
+      <c r="E203">
+        <v>3.779999999999994</v>
+      </c>
+      <c r="F203">
+        <v>59.52380952</v>
+      </c>
+      <c r="G203" t="s">
+        <v>9</v>
+      </c>
+      <c r="I203" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>14</v>
+      </c>
+      <c r="C204">
+        <v>687.5</v>
+      </c>
+      <c r="D204">
+        <v>48.411517000000003</v>
+      </c>
+      <c r="E204">
+        <v>3.7599990000000005</v>
+      </c>
+      <c r="F204">
+        <v>59.84044145</v>
+      </c>
+      <c r="G204" t="s">
+        <v>9</v>
+      </c>
+      <c r="I204" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>14</v>
+      </c>
+      <c r="C205">
+        <v>750</v>
+      </c>
+      <c r="D205">
+        <v>52.171515999999997</v>
+      </c>
+      <c r="E205">
+        <v>3.7599990000000005</v>
+      </c>
+      <c r="F205">
+        <v>59.84044145</v>
+      </c>
+      <c r="G205" t="s">
+        <v>9</v>
+      </c>
+      <c r="I205" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>14</v>
+      </c>
+      <c r="C206">
+        <v>812.5</v>
+      </c>
+      <c r="D206">
+        <v>55.951514000000003</v>
+      </c>
+      <c r="E206">
+        <v>3.7799979999999991</v>
+      </c>
+      <c r="F206">
+        <v>59.523841019999999</v>
+      </c>
+      <c r="G206" t="s">
+        <v>9</v>
+      </c>
+      <c r="I206" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>14</v>
+      </c>
+      <c r="C207">
+        <v>875</v>
+      </c>
+      <c r="D207">
+        <v>59.731513999999997</v>
+      </c>
+      <c r="E207">
+        <v>3.7800000000000011</v>
+      </c>
+      <c r="F207">
+        <v>59.52380952</v>
+      </c>
+      <c r="G207" t="s">
+        <v>9</v>
+      </c>
+      <c r="I207" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>14</v>
+      </c>
+      <c r="C208">
+        <v>937.5</v>
+      </c>
+      <c r="D208">
+        <v>63.491514000000002</v>
+      </c>
+      <c r="E208">
+        <v>3.7600000000000051</v>
+      </c>
+      <c r="F208">
+        <v>59.840425529999997</v>
+      </c>
+      <c r="G208" t="s">
+        <v>9</v>
+      </c>
+      <c r="I208" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>14</v>
+      </c>
+      <c r="C209">
+        <v>1000</v>
+      </c>
+      <c r="D209">
+        <v>67.231514000000004</v>
+      </c>
+      <c r="E209">
+        <v>3.7399999999999949</v>
+      </c>
+      <c r="F209">
+        <v>60.160427810000002</v>
+      </c>
+      <c r="G209" t="s">
+        <v>9</v>
+      </c>
+      <c r="I209" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210">
+        <v>1062.5</v>
+      </c>
+      <c r="D210">
+        <v>70.971513999999999</v>
+      </c>
+      <c r="E210">
+        <v>3.7399999999999949</v>
+      </c>
+      <c r="F210">
+        <v>60.160427810000002</v>
+      </c>
+      <c r="G210" t="s">
+        <v>9</v>
+      </c>
+      <c r="I210" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>14</v>
+      </c>
+      <c r="C211">
+        <v>1125</v>
+      </c>
+      <c r="D211">
+        <v>74.731513000000007</v>
+      </c>
+      <c r="E211">
+        <v>3.7599990000000076</v>
+      </c>
+      <c r="F211">
+        <v>59.84044145</v>
+      </c>
+      <c r="G211" t="s">
+        <v>9</v>
+      </c>
+      <c r="I211" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212">
+        <v>1187.5</v>
+      </c>
+      <c r="D212">
+        <v>78.471513000000002</v>
+      </c>
+      <c r="E212">
+        <v>3.7399999999999949</v>
+      </c>
+      <c r="F212">
+        <v>60.160427810000002</v>
+      </c>
+      <c r="G212" t="s">
+        <v>9</v>
+      </c>
+      <c r="I212" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213">
+        <v>1250</v>
+      </c>
+      <c r="D213">
+        <v>82.211511999999999</v>
+      </c>
+      <c r="E213">
+        <v>3.7399989999999974</v>
+      </c>
+      <c r="F213">
+        <v>60.160443890000003</v>
+      </c>
+      <c r="G213" t="s">
+        <v>9</v>
+      </c>
+      <c r="I213" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214">
+        <v>1312.5</v>
+      </c>
+      <c r="D214">
+        <v>86.011510000000001</v>
+      </c>
+      <c r="E214">
+        <v>3.7999980000000022</v>
+      </c>
+      <c r="F214">
+        <v>59.210557479999999</v>
+      </c>
+      <c r="G214" t="s">
+        <v>9</v>
+      </c>
+      <c r="I214" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215">
+        <v>1375</v>
+      </c>
+      <c r="D215">
+        <v>89.791509000000005</v>
+      </c>
+      <c r="E215">
+        <v>3.7799990000000037</v>
+      </c>
+      <c r="F215">
+        <v>59.523825270000003</v>
+      </c>
+      <c r="G215" t="s">
+        <v>9</v>
+      </c>
+      <c r="I215" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216">
+        <v>1437.5</v>
+      </c>
+      <c r="D216">
+        <v>93.611508000000001</v>
+      </c>
+      <c r="E216">
+        <v>3.8199989999999957</v>
+      </c>
+      <c r="F216">
+        <v>58.90053898</v>
+      </c>
+      <c r="G216" t="s">
+        <v>9</v>
+      </c>
+      <c r="I216" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>14</v>
+      </c>
+      <c r="C217">
+        <v>1500</v>
+      </c>
+      <c r="D217">
+        <v>97.431506999999996</v>
+      </c>
+      <c r="E217">
+        <v>3.8199990000000099</v>
+      </c>
+      <c r="F217">
+        <v>58.90053898</v>
+      </c>
+      <c r="G217" t="s">
+        <v>9</v>
+      </c>
+      <c r="I217" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>14</v>
+      </c>
+      <c r="C218">
+        <v>1562.5</v>
+      </c>
+      <c r="D218">
+        <v>101.271507</v>
+      </c>
+      <c r="E218">
+        <v>3.8399999999999892</v>
+      </c>
+      <c r="F218">
+        <v>58.59375</v>
+      </c>
+      <c r="G218" t="s">
+        <v>9</v>
+      </c>
+      <c r="I218" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>14</v>
+      </c>
+      <c r="C219">
+        <v>1625</v>
+      </c>
+      <c r="D219">
+        <v>105.151506</v>
+      </c>
+      <c r="E219">
+        <v>3.8799990000000122</v>
+      </c>
+      <c r="F219">
+        <v>57.989705669999999</v>
+      </c>
+      <c r="G219" t="s">
+        <v>9</v>
+      </c>
+      <c r="I219" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>14</v>
+      </c>
+      <c r="C220">
+        <v>1687.5</v>
+      </c>
+      <c r="D220">
+        <v>109.011506</v>
+      </c>
+      <c r="E220">
+        <v>3.8599999999999994</v>
+      </c>
+      <c r="F220">
+        <v>58.290155439999999</v>
+      </c>
+      <c r="G220" t="s">
+        <v>9</v>
+      </c>
+      <c r="I220" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>14</v>
+      </c>
+      <c r="C221">
+        <v>1750</v>
+      </c>
+      <c r="D221">
+        <v>112.89150600000001</v>
+      </c>
+      <c r="E221">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F221">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G221" t="s">
+        <v>9</v>
+      </c>
+      <c r="I221" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>14</v>
+      </c>
+      <c r="C222">
+        <v>1812.5</v>
+      </c>
+      <c r="D222">
+        <v>116.791505</v>
+      </c>
+      <c r="E222">
+        <v>3.899998999999994</v>
+      </c>
+      <c r="F222">
+        <v>57.692322490000002</v>
+      </c>
+      <c r="G222" t="s">
+        <v>9</v>
+      </c>
+      <c r="I222" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223">
+        <v>1875</v>
+      </c>
+      <c r="D223">
+        <v>120.71150299999999</v>
+      </c>
+      <c r="E223">
+        <v>3.9199980000000068</v>
+      </c>
+      <c r="F223">
+        <v>57.397988470000001</v>
+      </c>
+      <c r="G223" t="s">
+        <v>9</v>
+      </c>
+      <c r="I223" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224">
+        <v>1937.5</v>
+      </c>
+      <c r="D224">
+        <v>124.631501</v>
+      </c>
+      <c r="E224">
+        <v>3.9199979999999925</v>
+      </c>
+      <c r="F224">
+        <v>57.397988470000001</v>
+      </c>
+      <c r="G224" t="s">
+        <v>9</v>
+      </c>
+      <c r="I224" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>14</v>
+      </c>
+      <c r="C225">
+        <v>2000</v>
+      </c>
+      <c r="D225">
+        <v>128.61150000000001</v>
+      </c>
+      <c r="E225">
+        <v>3.9799989999999923</v>
+      </c>
+      <c r="F225">
+        <v>56.53267752</v>
+      </c>
+      <c r="G225" t="s">
+        <v>9</v>
+      </c>
+      <c r="I225" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226">
+        <v>2062.5</v>
+      </c>
+      <c r="D226">
+        <v>132.57149899999999</v>
+      </c>
+      <c r="E226">
+        <v>3.9599990000000105</v>
+      </c>
+      <c r="F226">
+        <v>56.81819617</v>
+      </c>
+      <c r="G226" t="s">
+        <v>9</v>
+      </c>
+      <c r="I226" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227">
+        <v>2125</v>
+      </c>
+      <c r="D227">
+        <v>136.55149900000001</v>
+      </c>
+      <c r="E227">
+        <v>3.9799999999999898</v>
+      </c>
+      <c r="F227">
+        <v>56.532663319999997</v>
+      </c>
+      <c r="G227" t="s">
+        <v>9</v>
+      </c>
+      <c r="I227" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228">
+        <v>2187.5</v>
+      </c>
+      <c r="D228">
+        <v>140.57149799999999</v>
+      </c>
+      <c r="E228">
+        <v>4.0199990000000128</v>
+      </c>
+      <c r="F228">
+        <v>55.97016318</v>
+      </c>
+      <c r="G228" t="s">
+        <v>9</v>
+      </c>
+      <c r="I228" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229">
+        <v>2250</v>
+      </c>
+      <c r="D229">
+        <v>144.57149799999999</v>
+      </c>
+      <c r="E229">
+        <v>4</v>
+      </c>
+      <c r="F229">
+        <v>56.25</v>
+      </c>
+      <c r="G229" t="s">
+        <v>9</v>
+      </c>
+      <c r="I229" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>14</v>
+      </c>
+      <c r="C230">
+        <v>2312.5</v>
+      </c>
+      <c r="D230">
+        <v>148.591498</v>
+      </c>
+      <c r="E230">
+        <v>4.0200000000000102</v>
+      </c>
+      <c r="F230">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G230" t="s">
+        <v>9</v>
+      </c>
+      <c r="I230" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>14</v>
+      </c>
+      <c r="C231">
+        <v>2375</v>
+      </c>
+      <c r="D231">
+        <v>152.63149799999999</v>
+      </c>
+      <c r="E231">
+        <v>4.039999999999992</v>
+      </c>
+      <c r="F231">
+        <v>55.693069309999998</v>
+      </c>
+      <c r="G231" t="s">
+        <v>9</v>
+      </c>
+      <c r="I231" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232">
+        <v>2437.5</v>
+      </c>
+      <c r="D232">
+        <v>156.67149800000001</v>
+      </c>
+      <c r="E232">
+        <v>4.039999999999992</v>
+      </c>
+      <c r="F232">
+        <v>55.693069309999998</v>
+      </c>
+      <c r="G232" t="s">
+        <v>9</v>
+      </c>
+      <c r="I232" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233">
+        <v>2500</v>
+      </c>
+      <c r="D233">
+        <v>160.73149799999999</v>
+      </c>
+      <c r="E233">
+        <v>4.0600000000000023</v>
+      </c>
+      <c r="F233">
+        <v>55.418719209999999</v>
+      </c>
+      <c r="G233" t="s">
+        <v>9</v>
+      </c>
+      <c r="I233" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234">
+        <v>2562.5</v>
+      </c>
+      <c r="D234">
+        <v>164.811498</v>
+      </c>
+      <c r="E234">
+        <v>4.0800000000000125</v>
+      </c>
+      <c r="F234">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G234" t="s">
+        <v>9</v>
+      </c>
+      <c r="I234" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235">
+        <v>2625</v>
+      </c>
+      <c r="D235">
+        <v>168.89149800000001</v>
+      </c>
+      <c r="E235">
+        <v>4.0799999999999841</v>
+      </c>
+      <c r="F235">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G235" t="s">
+        <v>9</v>
+      </c>
+      <c r="I235" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236">
+        <v>2687.5</v>
+      </c>
+      <c r="D236">
+        <v>172.99149800000001</v>
+      </c>
+      <c r="E236">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F236">
+        <v>54.87804878</v>
+      </c>
+      <c r="G236" t="s">
+        <v>9</v>
+      </c>
+      <c r="I236" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237">
+        <v>2750</v>
+      </c>
+      <c r="D237">
+        <v>177.091497</v>
+      </c>
+      <c r="E237">
+        <v>4.0999990000000253</v>
+      </c>
+      <c r="F237">
+        <v>54.87806217</v>
+      </c>
+      <c r="G237" t="s">
+        <v>9</v>
+      </c>
+      <c r="I237" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>14</v>
+      </c>
+      <c r="C238">
+        <v>2812.5</v>
+      </c>
+      <c r="D238">
+        <v>181.191497</v>
+      </c>
+      <c r="E238">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F238">
+        <v>54.87804878</v>
+      </c>
+      <c r="G238" t="s">
+        <v>9</v>
+      </c>
+      <c r="I238" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239">
+        <v>2875</v>
+      </c>
+      <c r="D239">
+        <v>185.311497</v>
+      </c>
+      <c r="E239">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F239">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G239" t="s">
+        <v>9</v>
+      </c>
+      <c r="I239" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>14</v>
+      </c>
+      <c r="C240">
+        <v>2937.5</v>
+      </c>
+      <c r="D240">
+        <v>189.45149699999999</v>
+      </c>
+      <c r="E240">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F240">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G240" t="s">
+        <v>9</v>
+      </c>
+      <c r="I240" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>14</v>
+      </c>
+      <c r="C241">
+        <v>3000</v>
+      </c>
+      <c r="D241">
+        <v>193.61149599999999</v>
+      </c>
+      <c r="E241">
+        <v>4.1599989999999991</v>
+      </c>
+      <c r="F241">
+        <v>54.086551460000003</v>
+      </c>
+      <c r="G241" t="s">
+        <v>9</v>
+      </c>
+      <c r="I241" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242">
+        <v>3062.5</v>
+      </c>
+      <c r="D242">
+        <v>197.75149500000001</v>
+      </c>
+      <c r="E242">
+        <v>4.1399990000000173</v>
+      </c>
+      <c r="F242">
+        <v>54.347839209999997</v>
+      </c>
+      <c r="G242" t="s">
+        <v>9</v>
+      </c>
+      <c r="I242" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>14</v>
+      </c>
+      <c r="C243">
+        <v>3125</v>
+      </c>
+      <c r="D243">
+        <v>201.87149500000001</v>
+      </c>
+      <c r="E243">
+        <v>4.1199999999999761</v>
+      </c>
+      <c r="F243">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G243" t="s">
+        <v>9</v>
+      </c>
+      <c r="I243" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244">
+        <v>3187.5</v>
+      </c>
+      <c r="D244">
+        <v>205.97149400000001</v>
+      </c>
+      <c r="E244">
+        <v>4.0999989999999968</v>
+      </c>
+      <c r="F244">
+        <v>54.87806217</v>
+      </c>
+      <c r="G244" t="s">
+        <v>9</v>
+      </c>
+      <c r="I244" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>14</v>
+      </c>
+      <c r="C245">
+        <v>3250</v>
+      </c>
+      <c r="D245">
+        <v>210.071493</v>
+      </c>
+      <c r="E245">
+        <v>4.0999990000000253</v>
+      </c>
+      <c r="F245">
+        <v>54.87806217</v>
+      </c>
+      <c r="G245" t="s">
+        <v>9</v>
+      </c>
+      <c r="I245" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>14</v>
+      </c>
+      <c r="C246">
+        <v>3312.5</v>
+      </c>
+      <c r="D246">
+        <v>214.171493</v>
+      </c>
+      <c r="E246">
+        <v>4.0999999999999943</v>
+      </c>
+      <c r="F246">
+        <v>54.87804878</v>
+      </c>
+      <c r="G246" t="s">
+        <v>9</v>
+      </c>
+      <c r="I246" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>14</v>
+      </c>
+      <c r="C247">
+        <v>3375</v>
+      </c>
+      <c r="D247">
+        <v>218.25149300000001</v>
+      </c>
+      <c r="E247">
+        <v>4.0799999999999841</v>
+      </c>
+      <c r="F247">
+        <v>55.147058819999998</v>
+      </c>
+      <c r="G247" t="s">
+        <v>9</v>
+      </c>
+      <c r="I247" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>14</v>
+      </c>
+      <c r="C248">
+        <v>3437.5</v>
+      </c>
+      <c r="D248">
+        <v>222.37149299999999</v>
+      </c>
+      <c r="E248">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F248">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G248" t="s">
+        <v>9</v>
+      </c>
+      <c r="I248" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>14</v>
+      </c>
+      <c r="C249">
+        <v>3500</v>
+      </c>
+      <c r="D249">
+        <v>226.49149299999999</v>
+      </c>
+      <c r="E249">
+        <v>4.1200000000000045</v>
+      </c>
+      <c r="F249">
+        <v>54.611650490000002</v>
+      </c>
+      <c r="G249" t="s">
+        <v>9</v>
+      </c>
+      <c r="I249" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250">
+        <v>3562.5</v>
+      </c>
+      <c r="D250">
+        <v>230.63149300000001</v>
+      </c>
+      <c r="E250">
+        <v>4.1400000000000148</v>
+      </c>
+      <c r="F250">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G250" t="s">
+        <v>9</v>
+      </c>
+      <c r="I250" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>14</v>
+      </c>
+      <c r="C251">
+        <v>3625</v>
+      </c>
+      <c r="D251">
+        <v>234.77149299999999</v>
+      </c>
+      <c r="E251">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F251">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G251" t="s">
+        <v>9</v>
+      </c>
+      <c r="I251" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252">
+        <v>3687.5</v>
+      </c>
+      <c r="D252">
+        <v>238.91149300000001</v>
+      </c>
+      <c r="E252">
+        <v>4.1399999999999864</v>
+      </c>
+      <c r="F252">
+        <v>54.347826089999998</v>
+      </c>
+      <c r="G252" t="s">
+        <v>9</v>
+      </c>
+      <c r="I252" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253">
+        <v>3750</v>
+      </c>
+      <c r="D253">
+        <v>243.051492</v>
+      </c>
+      <c r="E253">
+        <v>4.1399990000000173</v>
+      </c>
+      <c r="F253">
+        <v>54.347839209999997</v>
+      </c>
+      <c r="G253" t="s">
+        <v>9</v>
+      </c>
+      <c r="I253" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254">
+        <v>3812.5</v>
+      </c>
+      <c r="D254">
+        <v>247.21149199999999</v>
+      </c>
+      <c r="E254">
+        <v>4.1599999999999966</v>
+      </c>
+      <c r="F254">
+        <v>54.08653846</v>
+      </c>
+      <c r="G254" t="s">
+        <v>9</v>
+      </c>
+      <c r="I254" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>14</v>
+      </c>
+      <c r="C255">
+        <v>3875</v>
+      </c>
+      <c r="D255">
+        <v>251.37149199999999</v>
+      </c>
+      <c r="E255">
+        <v>4.160000000000025</v>
+      </c>
+      <c r="F255">
+        <v>54.08653846</v>
+      </c>
+      <c r="G255" t="s">
+        <v>9</v>
+      </c>
+      <c r="I255" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256">
+        <v>3937.5</v>
+      </c>
+      <c r="D256">
+        <v>255.491491</v>
+      </c>
+      <c r="E256">
+        <v>4.1199989999999502</v>
+      </c>
+      <c r="F256">
+        <v>54.611663739999997</v>
+      </c>
+      <c r="G256" t="s">
+        <v>9</v>
+      </c>
+      <c r="I256" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>14</v>
+      </c>
+      <c r="C257">
+        <v>4000</v>
+      </c>
+      <c r="D257">
+        <v>259.65148799999997</v>
+      </c>
+      <c r="E257">
+        <v>4.1599970000000326</v>
+      </c>
+      <c r="F257">
+        <v>54.086577470000002</v>
+      </c>
+      <c r="G257" t="s">
+        <v>9</v>
+      </c>
+      <c r="I257" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>16</v>
+      </c>
+      <c r="C258">
+        <v>62.5</v>
+      </c>
+      <c r="D258">
+        <v>8.6799990000000005</v>
+      </c>
+      <c r="E258">
+        <v>8.6799990000000022</v>
+      </c>
+      <c r="F258">
+        <v>25.921661969999999</v>
+      </c>
+      <c r="G258" t="s">
+        <v>9</v>
+      </c>
+      <c r="I258" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>16</v>
+      </c>
+      <c r="C259">
+        <v>125</v>
+      </c>
+      <c r="D259">
+        <v>13.479651</v>
+      </c>
+      <c r="E259">
+        <v>4.7996519999999983</v>
+      </c>
+      <c r="F259">
+        <v>46.878398679999997</v>
+      </c>
+      <c r="G259" t="s">
+        <v>9</v>
+      </c>
+      <c r="I259" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>16</v>
+      </c>
+      <c r="C260">
+        <v>187.5</v>
+      </c>
+      <c r="D260">
+        <v>17.600925</v>
+      </c>
+      <c r="E260">
+        <v>4.1212739999999997</v>
+      </c>
+      <c r="F260">
+        <v>54.594768510000002</v>
+      </c>
+      <c r="G260" t="s">
+        <v>9</v>
+      </c>
+      <c r="I260" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>16</v>
+      </c>
+      <c r="C261">
+        <v>250</v>
+      </c>
+      <c r="D261">
+        <v>21.520921000000001</v>
+      </c>
+      <c r="E261">
+        <v>3.9199959999999976</v>
+      </c>
+      <c r="F261">
+        <v>57.398017750000001</v>
+      </c>
+      <c r="G261" t="s">
+        <v>9</v>
+      </c>
+      <c r="I261" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>16</v>
+      </c>
+      <c r="C262">
+        <v>312.5</v>
+      </c>
+      <c r="D262">
+        <v>25.300916000000001</v>
+      </c>
+      <c r="E262">
+        <v>3.7799949999999995</v>
+      </c>
+      <c r="F262">
+        <v>59.52388826</v>
+      </c>
+      <c r="G262" t="s">
+        <v>9</v>
+      </c>
+      <c r="I262" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>16</v>
+      </c>
+      <c r="C263">
+        <v>375</v>
+      </c>
+      <c r="D263">
+        <v>29.020913</v>
+      </c>
+      <c r="E263">
+        <v>3.7199970000000064</v>
+      </c>
+      <c r="F263">
+        <v>60.483919749999998</v>
+      </c>
+      <c r="G263" t="s">
+        <v>9</v>
+      </c>
+      <c r="I263" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>16</v>
+      </c>
+      <c r="C264">
+        <v>437.5</v>
+      </c>
+      <c r="D264">
+        <v>32.740912999999999</v>
+      </c>
+      <c r="E264">
+        <v>3.7199999999999989</v>
+      </c>
+      <c r="F264">
+        <v>60.483870969999998</v>
+      </c>
+      <c r="G264" t="s">
+        <v>9</v>
+      </c>
+      <c r="I264" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>16</v>
+      </c>
+      <c r="C265">
+        <v>500</v>
+      </c>
+      <c r="D265">
+        <v>36.420912000000001</v>
+      </c>
+      <c r="E265">
+        <v>3.6799989999999951</v>
+      </c>
+      <c r="F265">
+        <v>61.141320960000002</v>
+      </c>
+      <c r="G265" t="s">
+        <v>9</v>
+      </c>
+      <c r="I265" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>16</v>
+      </c>
+      <c r="C266">
+        <v>562.5</v>
+      </c>
+      <c r="D266">
+        <v>40.080911</v>
+      </c>
+      <c r="E266">
+        <v>3.6599990000000062</v>
+      </c>
+      <c r="F266">
+        <v>61.475426630000001</v>
+      </c>
+      <c r="G266" t="s">
+        <v>9</v>
+      </c>
+      <c r="I266" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>16</v>
+      </c>
+      <c r="C267">
+        <v>625</v>
+      </c>
+      <c r="D267">
+        <v>43.760911</v>
+      </c>
+      <c r="E267">
+        <v>3.6799999999999997</v>
+      </c>
+      <c r="F267">
+        <v>61.141304349999999</v>
+      </c>
+      <c r="G267" t="s">
+        <v>9</v>
+      </c>
+      <c r="I267" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>16</v>
+      </c>
+      <c r="C268">
+        <v>687.5</v>
+      </c>
+      <c r="D268">
+        <v>47.480910999999999</v>
+      </c>
+      <c r="E268">
+        <v>3.7199999999999989</v>
+      </c>
+      <c r="F268">
+        <v>60.483870969999998</v>
+      </c>
+      <c r="G268" t="s">
+        <v>9</v>
+      </c>
+      <c r="I268" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>16</v>
+      </c>
+      <c r="C269">
+        <v>750</v>
+      </c>
+      <c r="D269">
+        <v>51.180911000000002</v>
+      </c>
+      <c r="E269">
+        <v>3.6999999999999957</v>
+      </c>
+      <c r="F269">
+        <v>60.81081081</v>
+      </c>
+      <c r="G269" t="s">
+        <v>9</v>
+      </c>
+      <c r="I269" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>16</v>
+      </c>
+      <c r="C270">
+        <v>812.5</v>
+      </c>
+      <c r="D270">
+        <v>54.900908000000001</v>
+      </c>
+      <c r="E270">
+        <v>3.7199969999999993</v>
+      </c>
+      <c r="F270">
+        <v>60.483919749999998</v>
+      </c>
+      <c r="G270" t="s">
+        <v>9</v>
+      </c>
+      <c r="I270" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>16</v>
+      </c>
+      <c r="C271">
+        <v>875</v>
+      </c>
+      <c r="D271">
+        <v>58.620908</v>
+      </c>
+      <c r="E271">
+        <v>3.7199999999999989</v>
+      </c>
+      <c r="F271">
+        <v>60.483870969999998</v>
+      </c>
+      <c r="G271" t="s">
+        <v>9</v>
+      </c>
+      <c r="I271" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>16</v>
+      </c>
+      <c r="C272">
+        <v>937.5</v>
+      </c>
+      <c r="D272">
+        <v>62.380906000000003</v>
+      </c>
+      <c r="E272">
+        <v>3.7599980000000102</v>
+      </c>
+      <c r="F272">
+        <v>59.840457360000002</v>
+      </c>
+      <c r="G272" t="s">
+        <v>9</v>
+      </c>
+      <c r="I272" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>16</v>
+      </c>
+      <c r="C273">
+        <v>1000</v>
+      </c>
+      <c r="D273">
+        <v>66.120906000000005</v>
+      </c>
+      <c r="E273">
+        <v>3.7399999999999949</v>
+      </c>
+      <c r="F273">
+        <v>60.160427810000002</v>
+      </c>
+      <c r="G273" t="s">
+        <v>9</v>
+      </c>
+      <c r="I273" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>16</v>
+      </c>
+      <c r="C274">
+        <v>1062.5</v>
+      </c>
+      <c r="D274">
+        <v>69.860905000000002</v>
+      </c>
+      <c r="E274">
+        <v>3.7399989999999974</v>
+      </c>
+      <c r="F274">
+        <v>60.160443890000003</v>
+      </c>
+      <c r="G274" t="s">
+        <v>9</v>
+      </c>
+      <c r="I274" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>16</v>
+      </c>
+      <c r="C275">
+        <v>1125</v>
+      </c>
+      <c r="D275">
+        <v>73.600904999999997</v>
+      </c>
+      <c r="E275">
+        <v>3.7399999999999949</v>
+      </c>
+      <c r="F275">
+        <v>60.160427810000002</v>
+      </c>
+      <c r="G275" t="s">
+        <v>9</v>
+      </c>
+      <c r="I275" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>16</v>
+      </c>
+      <c r="C276">
+        <v>1187.5</v>
+      </c>
+      <c r="D276">
+        <v>77.440903000000006</v>
+      </c>
+      <c r="E276">
+        <v>3.8399980000000085</v>
+      </c>
+      <c r="F276">
+        <v>58.593780520000003</v>
+      </c>
+      <c r="G276" t="s">
+        <v>9</v>
+      </c>
+      <c r="I276" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>16</v>
+      </c>
+      <c r="C277">
+        <v>1250</v>
+      </c>
+      <c r="D277">
+        <v>81.260902999999999</v>
+      </c>
+      <c r="E277">
+        <v>3.8199999999999932</v>
+      </c>
+      <c r="F277">
+        <v>58.900523560000003</v>
+      </c>
+      <c r="G277" t="s">
+        <v>9</v>
+      </c>
+      <c r="I277" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>16</v>
+      </c>
+      <c r="C278">
+        <v>1312.5</v>
+      </c>
+      <c r="D278">
+        <v>85.000901999999996</v>
+      </c>
+      <c r="E278">
+        <v>3.7399990000000116</v>
+      </c>
+      <c r="F278">
+        <v>60.160443890000003</v>
+      </c>
+      <c r="G278" t="s">
+        <v>9</v>
+      </c>
+      <c r="I278" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>16</v>
+      </c>
+      <c r="C279">
+        <v>1375</v>
+      </c>
+      <c r="D279">
+        <v>88.780901999999998</v>
+      </c>
+      <c r="E279">
+        <v>3.7799999999999869</v>
+      </c>
+      <c r="F279">
+        <v>59.52380952</v>
+      </c>
+      <c r="G279" t="s">
+        <v>9</v>
+      </c>
+      <c r="I279" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>16</v>
+      </c>
+      <c r="C280">
+        <v>1437.5</v>
+      </c>
+      <c r="D280">
+        <v>92.560901999999999</v>
+      </c>
+      <c r="E280">
+        <v>3.7800000000000011</v>
+      </c>
+      <c r="F280">
+        <v>59.52380952</v>
+      </c>
+      <c r="G280" t="s">
+        <v>9</v>
+      </c>
+      <c r="I280" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>16</v>
+      </c>
+      <c r="C281">
+        <v>1500</v>
+      </c>
+      <c r="D281">
+        <v>96.380899999999997</v>
+      </c>
+      <c r="E281">
+        <v>3.8199980000000124</v>
+      </c>
+      <c r="F281">
+        <v>58.900554399999997</v>
+      </c>
+      <c r="G281" t="s">
+        <v>9</v>
+      </c>
+      <c r="I281" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>16</v>
+      </c>
+      <c r="C282">
+        <v>1562.5</v>
+      </c>
+      <c r="D282">
+        <v>100.2009</v>
+      </c>
+      <c r="E282">
+        <v>3.8199999999999932</v>
+      </c>
+      <c r="F282">
+        <v>58.900523560000003</v>
+      </c>
+      <c r="G282" t="s">
+        <v>9</v>
+      </c>
+      <c r="I282" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>16</v>
+      </c>
+      <c r="C283">
+        <v>1625</v>
+      </c>
+      <c r="D283">
+        <v>104.040899</v>
+      </c>
+      <c r="E283">
+        <v>3.8399990000000059</v>
+      </c>
+      <c r="F283">
+        <v>58.593765259999998</v>
+      </c>
+      <c r="G283" t="s">
+        <v>9</v>
+      </c>
+      <c r="I283" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>16</v>
+      </c>
+      <c r="C284">
+        <v>1687.5</v>
+      </c>
+      <c r="D284">
+        <v>107.880899</v>
+      </c>
+      <c r="E284">
+        <v>3.8399999999999892</v>
+      </c>
+      <c r="F284">
+        <v>58.59375</v>
+      </c>
+      <c r="G284" t="s">
+        <v>9</v>
+      </c>
+      <c r="I284" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>16</v>
+      </c>
+      <c r="C285">
+        <v>1750</v>
+      </c>
+      <c r="D285">
+        <v>111.70089900000001</v>
+      </c>
+      <c r="E285">
+        <v>3.8200000000000074</v>
+      </c>
+      <c r="F285">
+        <v>58.900523560000003</v>
+      </c>
+      <c r="G285" t="s">
+        <v>9</v>
+      </c>
+      <c r="I285" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>16</v>
+      </c>
+      <c r="C286">
+        <v>1812.5</v>
+      </c>
+      <c r="D286">
+        <v>115.580896</v>
+      </c>
+      <c r="E286">
+        <v>3.879997000000003</v>
+      </c>
+      <c r="F286">
+        <v>57.98973556</v>
+      </c>
+      <c r="G286" t="s">
+        <v>9</v>
+      </c>
+      <c r="I286" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>16</v>
+      </c>
+      <c r="C287">
+        <v>1875</v>
+      </c>
+      <c r="D287">
+        <v>119.420894</v>
+      </c>
+      <c r="E287">
+        <v>3.8399980000000085</v>
+      </c>
+      <c r="F287">
+        <v>58.593780520000003</v>
+      </c>
+      <c r="G287" t="s">
+        <v>9</v>
+      </c>
+      <c r="I287" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>16</v>
+      </c>
+      <c r="C288">
+        <v>1937.5</v>
+      </c>
+      <c r="D288">
+        <v>123.260893</v>
+      </c>
+      <c r="E288">
+        <v>3.8399989999999775</v>
+      </c>
+      <c r="F288">
+        <v>58.593765259999998</v>
+      </c>
+      <c r="G288" t="s">
+        <v>9</v>
+      </c>
+      <c r="I288" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>16</v>
+      </c>
+      <c r="C289">
+        <v>2000</v>
+      </c>
+      <c r="D289">
+        <v>127.120893</v>
+      </c>
+      <c r="E289">
+        <v>3.8600000000000136</v>
+      </c>
+      <c r="F289">
+        <v>58.290155439999999</v>
+      </c>
+      <c r="G289" t="s">
+        <v>9</v>
+      </c>
+      <c r="I289" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>16</v>
+      </c>
+      <c r="C290">
+        <v>2062.5</v>
+      </c>
+      <c r="D290">
+        <v>131.00089299999999</v>
+      </c>
+      <c r="E290">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F290">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G290" t="s">
+        <v>9</v>
+      </c>
+      <c r="I290" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>16</v>
+      </c>
+      <c r="C291">
+        <v>2125</v>
+      </c>
+      <c r="D291">
+        <v>134.88089299999999</v>
+      </c>
+      <c r="E291">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F291">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G291" t="s">
+        <v>9</v>
+      </c>
+      <c r="I291" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>16</v>
+      </c>
+      <c r="C292">
+        <v>2187.5</v>
+      </c>
+      <c r="D292">
+        <v>138.76089200000001</v>
+      </c>
+      <c r="E292">
+        <v>3.879998999999998</v>
+      </c>
+      <c r="F292">
+        <v>57.989705669999999</v>
+      </c>
+      <c r="G292" t="s">
+        <v>9</v>
+      </c>
+      <c r="I292" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>16</v>
+      </c>
+      <c r="C293">
+        <v>2250</v>
+      </c>
+      <c r="D293">
+        <v>142.64089200000001</v>
+      </c>
+      <c r="E293">
+        <v>3.8799999999999955</v>
+      </c>
+      <c r="F293">
+        <v>57.989690719999999</v>
+      </c>
+      <c r="G293" t="s">
+        <v>9</v>
+      </c>
+      <c r="I293" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>16</v>
+      </c>
+      <c r="C294">
+        <v>2312.5</v>
+      </c>
+      <c r="D294">
+        <v>146.54089200000001</v>
+      </c>
+      <c r="E294">
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="F294">
+        <v>57.69230769</v>
+      </c>
+      <c r="G294" t="s">
+        <v>9</v>
+      </c>
+      <c r="I294" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>16</v>
+      </c>
+      <c r="C295">
+        <v>2375</v>
+      </c>
+      <c r="D295">
+        <v>150.400891</v>
+      </c>
+      <c r="E295">
+        <v>3.8599990000000162</v>
+      </c>
+      <c r="F295">
+        <v>58.290170539999998</v>
+      </c>
+      <c r="G295" t="s">
+        <v>9</v>
+      </c>
+      <c r="I295" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>16</v>
+      </c>
+      <c r="C296">
+        <v>2437.5</v>
+      </c>
+      <c r="D296">
+        <v>154.30089100000001</v>
+      </c>
+      <c r="E296">
+        <v>3.8999999999999773</v>
+      </c>
+      <c r="F296">
+        <v>57.69230769</v>
+      </c>
+      <c r="G296" t="s">
+        <v>9</v>
+      </c>
+      <c r="I296" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>16</v>
+      </c>
+      <c r="C297">
+        <v>2500</v>
+      </c>
+      <c r="D297">
+        <v>158.20089100000001</v>
+      </c>
+      <c r="E297">
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="F297">
+        <v>57.69230769</v>
+      </c>
+      <c r="G297" t="s">
+        <v>9</v>
+      </c>
+      <c r="I297" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>16</v>
+      </c>
+      <c r="C298">
+        <v>2562.5</v>
+      </c>
+      <c r="D298">
+        <v>162.10089099999999</v>
+      </c>
+      <c r="E298">
+        <v>3.9000000000000057</v>
+      </c>
+      <c r="F298">
+        <v>57.69230769</v>
+      </c>
+      <c r="G298" t="s">
+        <v>9</v>
+      </c>
+      <c r="I298" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>16</v>
+      </c>
+      <c r="C299">
+        <v>2625</v>
+      </c>
+      <c r="D299">
+        <v>166.02089100000001</v>
+      </c>
+      <c r="E299">
+        <v>3.9199999999999875</v>
+      </c>
+      <c r="F299">
+        <v>57.397959180000001</v>
+      </c>
+      <c r="G299" t="s">
+        <v>9</v>
+      </c>
+      <c r="I299" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>16</v>
+      </c>
+      <c r="C300">
+        <v>2687.5</v>
+      </c>
+      <c r="D300">
+        <v>169.96089000000001</v>
+      </c>
+      <c r="E300">
+        <v>3.9399990000000003</v>
+      </c>
+      <c r="F300">
+        <v>57.10661348</v>
+      </c>
+      <c r="G300" t="s">
+        <v>9</v>
+      </c>
+      <c r="I300" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>16</v>
+      </c>
+      <c r="C301">
+        <v>2750</v>
+      </c>
+      <c r="D301">
+        <v>173.90089</v>
+      </c>
+      <c r="E301">
+        <v>3.9400000000000261</v>
+      </c>
+      <c r="F301">
+        <v>57.106598980000001</v>
+      </c>
+      <c r="G301" t="s">
+        <v>9</v>
+      </c>
+      <c r="I301" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>16</v>
+      </c>
+      <c r="C302">
+        <v>2812.5</v>
+      </c>
+      <c r="D302">
+        <v>177.86089000000001</v>
+      </c>
+      <c r="E302">
+        <v>3.9599999999999795</v>
+      </c>
+      <c r="F302">
+        <v>56.81818182</v>
+      </c>
+      <c r="G302" t="s">
+        <v>9</v>
+      </c>
+      <c r="I302" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>16</v>
+      </c>
+      <c r="C303">
+        <v>2875</v>
+      </c>
+      <c r="D303">
+        <v>181.82088999999999</v>
+      </c>
+      <c r="E303">
+        <v>3.960000000000008</v>
+      </c>
+      <c r="F303">
+        <v>56.81818182</v>
+      </c>
+      <c r="G303" t="s">
+        <v>9</v>
+      </c>
+      <c r="I303" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>16</v>
+      </c>
+      <c r="C304">
+        <v>2937.5</v>
+      </c>
+      <c r="D304">
+        <v>185.78089</v>
+      </c>
+      <c r="E304">
+        <v>3.960000000000008</v>
+      </c>
+      <c r="F304">
+        <v>56.81818182</v>
+      </c>
+      <c r="G304" t="s">
+        <v>9</v>
+      </c>
+      <c r="I304" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>16</v>
+      </c>
+      <c r="C305">
+        <v>3000</v>
+      </c>
+      <c r="D305">
+        <v>189.76088999999999</v>
+      </c>
+      <c r="E305">
+        <v>3.9799999999999898</v>
+      </c>
+      <c r="F305">
+        <v>56.532663319999997</v>
+      </c>
+      <c r="G305" t="s">
+        <v>9</v>
+      </c>
+      <c r="I305" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>16</v>
+      </c>
+      <c r="C306">
+        <v>3062.5</v>
+      </c>
+      <c r="D306">
+        <v>193.74089000000001</v>
+      </c>
+      <c r="E306">
+        <v>3.9799999999999898</v>
+      </c>
+      <c r="F306">
+        <v>56.532663319999997</v>
+      </c>
+      <c r="G306" t="s">
+        <v>9</v>
+      </c>
+      <c r="I306" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>16</v>
+      </c>
+      <c r="C307">
+        <v>3125</v>
+      </c>
+      <c r="D307">
+        <v>197.720889</v>
+      </c>
+      <c r="E307">
+        <v>3.9799990000000207</v>
+      </c>
+      <c r="F307">
+        <v>56.53267752</v>
+      </c>
+      <c r="G307" t="s">
+        <v>9</v>
+      </c>
+      <c r="I307" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>16</v>
+      </c>
+      <c r="C308">
+        <v>3187.5</v>
+      </c>
+      <c r="D308">
+        <v>201.70088899999999</v>
+      </c>
+      <c r="E308">
+        <v>3.9799999999999898</v>
+      </c>
+      <c r="F308">
+        <v>56.532663319999997</v>
+      </c>
+      <c r="G308" t="s">
+        <v>9</v>
+      </c>
+      <c r="I308" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>16</v>
+      </c>
+      <c r="C309">
+        <v>3250</v>
+      </c>
+      <c r="D309">
+        <v>205.68088900000001</v>
+      </c>
+      <c r="E309">
+        <v>3.9799999999999898</v>
+      </c>
+      <c r="F309">
+        <v>56.532663319999997</v>
+      </c>
+      <c r="G309" t="s">
+        <v>9</v>
+      </c>
+      <c r="I309" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>16</v>
+      </c>
+      <c r="C310">
+        <v>3312.5</v>
+      </c>
+      <c r="D310">
+        <v>209.660888</v>
+      </c>
+      <c r="E310">
+        <v>3.9799990000000207</v>
+      </c>
+      <c r="F310">
+        <v>56.53267752</v>
+      </c>
+      <c r="G310" t="s">
+        <v>9</v>
+      </c>
+      <c r="I310" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>16</v>
+      </c>
+      <c r="C311">
+        <v>3375</v>
+      </c>
+      <c r="D311">
+        <v>213.660888</v>
+      </c>
+      <c r="E311">
+        <v>4</v>
+      </c>
+      <c r="F311">
+        <v>56.25</v>
+      </c>
+      <c r="G311" t="s">
+        <v>9</v>
+      </c>
+      <c r="I311" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>16</v>
+      </c>
+      <c r="C312">
+        <v>3437.5</v>
+      </c>
+      <c r="D312">
+        <v>217.660888</v>
+      </c>
+      <c r="E312">
+        <v>4</v>
+      </c>
+      <c r="F312">
+        <v>56.25</v>
+      </c>
+      <c r="G312" t="s">
+        <v>9</v>
+      </c>
+      <c r="I312" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>16</v>
+      </c>
+      <c r="C313">
+        <v>3500</v>
+      </c>
+      <c r="D313">
+        <v>221.68088800000001</v>
+      </c>
+      <c r="E313">
+        <v>4.0199999999999818</v>
+      </c>
+      <c r="F313">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G313" t="s">
+        <v>9</v>
+      </c>
+      <c r="I313" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>16</v>
+      </c>
+      <c r="C314">
+        <v>3562.5</v>
+      </c>
+      <c r="D314">
+        <v>225.720888</v>
+      </c>
+      <c r="E314">
+        <v>4.0400000000000205</v>
+      </c>
+      <c r="F314">
+        <v>55.693069309999998</v>
+      </c>
+      <c r="G314" t="s">
+        <v>9</v>
+      </c>
+      <c r="I314" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>16</v>
+      </c>
+      <c r="C315">
+        <v>3625</v>
+      </c>
+      <c r="D315">
+        <v>229.74088800000001</v>
+      </c>
+      <c r="E315">
+        <v>4.0199999999999818</v>
+      </c>
+      <c r="F315">
+        <v>55.970149249999999</v>
+      </c>
+      <c r="G315" t="s">
+        <v>9</v>
+      </c>
+      <c r="I315" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>16</v>
+      </c>
+      <c r="C316">
+        <v>3687.5</v>
+      </c>
+      <c r="D316">
+        <v>233.780888</v>
+      </c>
+      <c r="E316">
+        <v>4.039999999999992</v>
+      </c>
+      <c r="F316">
+        <v>55.693069309999998</v>
+      </c>
+      <c r="G316" t="s">
+        <v>9</v>
+      </c>
+      <c r="I316" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>16</v>
+      </c>
+      <c r="C317">
+        <v>3750</v>
+      </c>
+      <c r="D317">
+        <v>237.84088700000001</v>
+      </c>
+      <c r="E317">
+        <v>4.0599990000000048</v>
+      </c>
+      <c r="F317">
+        <v>55.418732859999999</v>
+      </c>
+      <c r="G317" t="s">
+        <v>9</v>
+      </c>
+      <c r="I317" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>16</v>
+      </c>
+      <c r="C318">
+        <v>3812.5</v>
+      </c>
+      <c r="D318">
+        <v>241.86088599999999</v>
+      </c>
+      <c r="E318">
+        <v>4.0199990000000128</v>
+      </c>
+      <c r="F318">
+        <v>55.97016318</v>
+      </c>
+      <c r="G318" t="s">
+        <v>9</v>
+      </c>
+      <c r="I318" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>16</v>
+      </c>
+      <c r="C319">
+        <v>3875</v>
+      </c>
+      <c r="D319">
+        <v>245.920884</v>
+      </c>
+      <c r="E319">
+        <v>4.0599979999999789</v>
+      </c>
+      <c r="F319">
+        <v>55.418746509999998</v>
+      </c>
+      <c r="G319" t="s">
+        <v>9</v>
+      </c>
+      <c r="I319" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>16</v>
+      </c>
+      <c r="C320">
+        <v>3937.5</v>
+      </c>
+      <c r="D320">
+        <v>250.00088099999999</v>
+      </c>
+      <c r="E320">
+        <v>4.0799969999999917</v>
+      </c>
+      <c r="F320">
+        <v>55.147099369999999</v>
+      </c>
+      <c r="G320" t="s">
+        <v>9</v>
+      </c>
+      <c r="I320" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>16</v>
+      </c>
+      <c r="C321">
+        <v>4000</v>
+      </c>
+      <c r="D321">
+        <v>254.060879</v>
+      </c>
+      <c r="E321">
+        <v>4.0599980000000073</v>
+      </c>
+      <c r="F321">
+        <v>55.418746509999998</v>
+      </c>
+      <c r="G321" t="s">
+        <v>9</v>
+      </c>
+      <c r="I321" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3437,5 +7623,8 @@
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:I193 A194:A321 I194:I321" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/pages/video_analysis/IP_Master_Men.xlsx
+++ b/pages/video_analysis/IP_Master_Men.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportnzgroup-my.sharepoint.com/personal/anja_kuys_hpsnz_org_nz/Documents/Desktop/Scripts/CNZPD/pages/video_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_F1FC6792D89E629903ED24B2C9460C765188C8B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D1CB14-47C1-4953-96E7-B64BD2730C23}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_F1FC6792D89E629903ED24B2C9460C765188C8B3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD742A7-85B4-4B4C-A004-06A21C31CBA8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="20">
   <si>
     <t>Title</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>26-07-31 Glasgow CWG Morton Q</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qCTIxXtG0Lg</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yjVZcfO11qw</t>
+  </si>
+  <si>
+    <t>https://youtu.be/z7zcj4I4qic</t>
   </si>
 </sst>
 </file>
@@ -413,12 +422,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I321"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -444,7 +453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -470,7 +479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -493,7 +502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -516,7 +525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -539,7 +548,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -562,7 +571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -585,7 +594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -608,7 +617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -631,7 +640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -654,7 +663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -677,7 +686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -700,7 +709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -723,7 +732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -746,7 +755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -769,7 +778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -792,7 +801,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -815,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -838,7 +847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -861,7 +870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -884,7 +893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -907,7 +916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -930,7 +939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -953,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -976,7 +985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -999,7 +1008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -1022,7 +1031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1045,7 +1054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1068,7 +1077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -1091,7 +1100,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -1114,7 +1123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -1137,7 +1146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1160,7 +1169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -1183,7 +1192,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -1206,7 +1215,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1229,7 +1238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1261,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -1275,7 +1284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -1298,7 +1307,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -1344,7 +1353,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1367,7 +1376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -1390,7 +1399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -1436,7 +1445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -1482,7 +1491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -1505,7 +1514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1537,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1551,7 +1560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -1574,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -1597,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1629,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -1643,7 +1652,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -1666,7 +1675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1689,7 +1698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -1712,7 +1721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -1735,7 +1744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -1758,7 +1767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -1781,7 +1790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -1804,7 +1813,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -1827,7 +1836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -1850,7 +1859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -1873,7 +1882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -1896,7 +1905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -1919,7 +1928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -1945,7 +1954,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -1968,7 +1977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -1991,7 +2000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -2014,7 +2023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -2037,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -2060,7 +2069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -2083,7 +2092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -2106,7 +2115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -2129,7 +2138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -2152,7 +2161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -2175,7 +2184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -2198,7 +2207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -2221,7 +2230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -2244,7 +2253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -2267,7 +2276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2290,7 +2299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -2313,7 +2322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -2336,7 +2345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -2359,7 +2368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -2382,7 +2391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -2405,7 +2414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -2428,7 +2437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -2451,7 +2460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -2474,7 +2483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -2497,7 +2506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -2520,7 +2529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -2543,7 +2552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -2566,7 +2575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -2589,7 +2598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -2612,7 +2621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -2635,7 +2644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -2658,7 +2667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -2681,7 +2690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2704,7 +2713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -2727,7 +2736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -2750,7 +2759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -2773,7 +2782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -2796,7 +2805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -2819,7 +2828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -2842,7 +2851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -2865,7 +2874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -2888,7 +2897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -2911,7 +2920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -2934,7 +2943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -2957,7 +2966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -2980,7 +2989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -3003,7 +3012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -3026,7 +3035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -3049,7 +3058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -3072,7 +3081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -3095,7 +3104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -3118,7 +3127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -3141,7 +3150,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -3164,7 +3173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -3187,7 +3196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -3210,7 +3219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -3233,7 +3242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -3256,7 +3265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -3279,7 +3288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -3302,7 +3311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -3325,7 +3334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -3348,7 +3357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -3371,7 +3380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -3394,7 +3403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -3413,8 +3422,11 @@
       <c r="G130" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -3434,7 +3446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -3454,7 +3466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -3474,7 +3486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -3494,7 +3506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -3514,7 +3526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -3534,7 +3546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -3554,7 +3566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -3574,7 +3586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -3594,7 +3606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -3614,7 +3626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -3634,7 +3646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -3654,7 +3666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>13</v>
       </c>
@@ -3674,7 +3686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -3694,7 +3706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -3714,7 +3726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>13</v>
       </c>
@@ -3734,7 +3746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -3754,7 +3766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>13</v>
       </c>
@@ -3774,7 +3786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -3794,7 +3806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>13</v>
       </c>
@@ -3814,7 +3826,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>13</v>
       </c>
@@ -3834,7 +3846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>13</v>
       </c>
@@ -3854,7 +3866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>13</v>
       </c>
@@ -3874,7 +3886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>13</v>
       </c>
@@ -3894,7 +3906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>13</v>
       </c>
@@ -3914,7 +3926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>13</v>
       </c>
@@ -3934,7 +3946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>13</v>
       </c>
@@ -3954,7 +3966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -3974,7 +3986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -3994,7 +4006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>13</v>
       </c>
@@ -4014,7 +4026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -4034,7 +4046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>13</v>
       </c>
@@ -4054,7 +4066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -4074,7 +4086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -4094,7 +4106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -4114,7 +4126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>13</v>
       </c>
@@ -4134,7 +4146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>13</v>
       </c>
@@ -4154,7 +4166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -4174,7 +4186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>13</v>
       </c>
@@ -4194,7 +4206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>13</v>
       </c>
@@ -4214,7 +4226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -4234,7 +4246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>13</v>
       </c>
@@ -4254,7 +4266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>13</v>
       </c>
@@ -4274,7 +4286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>13</v>
       </c>
@@ -4294,7 +4306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>13</v>
       </c>
@@ -4314,7 +4326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -4334,7 +4346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>13</v>
       </c>
@@ -4354,7 +4366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>13</v>
       </c>
@@ -4374,7 +4386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>13</v>
       </c>
@@ -4394,7 +4406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -4414,7 +4426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>13</v>
       </c>
@@ -4434,7 +4446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>13</v>
       </c>
@@ -4454,7 +4466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>13</v>
       </c>
@@ -4474,7 +4486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>13</v>
       </c>
@@ -4494,7 +4506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>13</v>
       </c>
@@ -4514,7 +4526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -4534,7 +4546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -4554,7 +4566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>13</v>
       </c>
@@ -4574,7 +4586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>13</v>
       </c>
@@ -4594,7 +4606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>13</v>
       </c>
@@ -4614,7 +4626,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -4634,7 +4646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -4654,7 +4666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -4674,7 +4686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>14</v>
       </c>
@@ -4693,11 +4705,14 @@
       <c r="G194" t="s">
         <v>9</v>
       </c>
+      <c r="H194" t="s">
+        <v>19</v>
+      </c>
       <c r="I194" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>14</v>
       </c>
@@ -4720,7 +4735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>14</v>
       </c>
@@ -4743,7 +4758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>14</v>
       </c>
@@ -4766,7 +4781,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>14</v>
       </c>
@@ -4789,7 +4804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>14</v>
       </c>
@@ -4812,7 +4827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>14</v>
       </c>
@@ -4835,7 +4850,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>14</v>
       </c>
@@ -4858,7 +4873,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>14</v>
       </c>
@@ -4881,7 +4896,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>14</v>
       </c>
@@ -4904,7 +4919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>14</v>
       </c>
@@ -4927,7 +4942,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>14</v>
       </c>
@@ -4950,7 +4965,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>14</v>
       </c>
@@ -4973,7 +4988,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>14</v>
       </c>
@@ -4996,7 +5011,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>14</v>
       </c>
@@ -5019,7 +5034,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>14</v>
       </c>
@@ -5042,7 +5057,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>14</v>
       </c>
@@ -5065,7 +5080,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>14</v>
       </c>
@@ -5088,7 +5103,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>14</v>
       </c>
@@ -5111,7 +5126,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>14</v>
       </c>
@@ -5134,7 +5149,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>14</v>
       </c>
@@ -5157,7 +5172,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>14</v>
       </c>
@@ -5180,7 +5195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>14</v>
       </c>
@@ -5203,7 +5218,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -5226,7 +5241,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>14</v>
       </c>
@@ -5249,7 +5264,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>14</v>
       </c>
@@ -5272,7 +5287,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>14</v>
       </c>
@@ -5295,7 +5310,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>14</v>
       </c>
@@ -5318,7 +5333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>14</v>
       </c>
@@ -5341,7 +5356,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>14</v>
       </c>
@@ -5364,7 +5379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>14</v>
       </c>
@@ -5387,7 +5402,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>14</v>
       </c>
@@ -5410,7 +5425,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>14</v>
       </c>
@@ -5433,7 +5448,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>14</v>
       </c>
@@ -5456,7 +5471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -5479,7 +5494,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -5502,7 +5517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -5525,7 +5540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>14</v>
       </c>
@@ -5548,7 +5563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -5571,7 +5586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>14</v>
       </c>
@@ -5594,7 +5609,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>14</v>
       </c>
@@ -5617,7 +5632,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>14</v>
       </c>
@@ -5640,7 +5655,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>14</v>
       </c>
@@ -5663,7 +5678,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>14</v>
       </c>
@@ -5686,7 +5701,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>14</v>
       </c>
@@ -5709,7 +5724,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -5732,7 +5747,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>14</v>
       </c>
@@ -5755,7 +5770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>14</v>
       </c>
@@ -5778,7 +5793,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>14</v>
       </c>
@@ -5801,7 +5816,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>14</v>
       </c>
@@ -5824,7 +5839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>14</v>
       </c>
@@ -5847,7 +5862,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>14</v>
       </c>
@@ -5870,7 +5885,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -5893,7 +5908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>14</v>
       </c>
@@ -5916,7 +5931,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>14</v>
       </c>
@@ -5939,7 +5954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>14</v>
       </c>
@@ -5962,7 +5977,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>14</v>
       </c>
@@ -5985,7 +6000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -6008,7 +6023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>14</v>
       </c>
@@ -6031,7 +6046,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>14</v>
       </c>
@@ -6054,7 +6069,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>14</v>
       </c>
@@ -6077,7 +6092,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>14</v>
       </c>
@@ -6100,7 +6115,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>14</v>
       </c>
@@ -6123,7 +6138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>14</v>
       </c>
@@ -6146,7 +6161,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -6165,11 +6180,14 @@
       <c r="G258" t="s">
         <v>9</v>
       </c>
+      <c r="H258" t="s">
+        <v>18</v>
+      </c>
       <c r="I258" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -6192,7 +6210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -6215,7 +6233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -6238,7 +6256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -6261,7 +6279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -6284,7 +6302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -6307,7 +6325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -6330,7 +6348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -6353,7 +6371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -6376,7 +6394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -6399,7 +6417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -6422,7 +6440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -6445,7 +6463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -6468,7 +6486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -6491,7 +6509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -6514,7 +6532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -6537,7 +6555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -6560,7 +6578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -6583,7 +6601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -6606,7 +6624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -6629,7 +6647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -6652,7 +6670,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -6675,7 +6693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -6698,7 +6716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -6721,7 +6739,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -6744,7 +6762,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -6767,7 +6785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -6790,7 +6808,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -6813,7 +6831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -6836,7 +6854,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -6859,7 +6877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -6882,7 +6900,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -6905,7 +6923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -6928,7 +6946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -6951,7 +6969,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>16</v>
       </c>
@@ -6974,7 +6992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>16</v>
       </c>
@@ -6997,7 +7015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>16</v>
       </c>
@@ -7020,7 +7038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>16</v>
       </c>
@@ -7043,7 +7061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>16</v>
       </c>
@@ -7066,7 +7084,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>16</v>
       </c>
@@ -7089,7 +7107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>16</v>
       </c>
@@ -7112,7 +7130,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>16</v>
       </c>
@@ -7135,7 +7153,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>16</v>
       </c>
@@ -7158,7 +7176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>16</v>
       </c>
@@ -7181,7 +7199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>16</v>
       </c>
@@ -7204,7 +7222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>16</v>
       </c>
@@ -7227,7 +7245,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>16</v>
       </c>
@@ -7250,7 +7268,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>16</v>
       </c>
@@ -7273,7 +7291,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>16</v>
       </c>
@@ -7296,7 +7314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>16</v>
       </c>
@@ -7319,7 +7337,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>16</v>
       </c>
@@ -7342,7 +7360,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>16</v>
       </c>
@@ -7365,7 +7383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>16</v>
       </c>
@@ -7388,7 +7406,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>16</v>
       </c>
@@ -7411,7 +7429,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>16</v>
       </c>
@@ -7434,7 +7452,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>16</v>
       </c>
@@ -7457,7 +7475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>16</v>
       </c>
@@ -7480,7 +7498,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>16</v>
       </c>
@@ -7503,7 +7521,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>16</v>
       </c>
@@ -7526,7 +7544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>16</v>
       </c>
@@ -7549,7 +7567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>16</v>
       </c>
@@ -7572,7 +7590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -7595,7 +7613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>16</v>
       </c>
@@ -7624,7 +7642,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I193 A194:A321 I194:I321" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:I129 A194:A321 I194:I321 A131:I193 A130:G130 I130" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>